--- a/data/processed/dados_limpos.xlsx
+++ b/data/processed/dados_limpos.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T577"/>
+  <dimension ref="A1:T574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,13 +535,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -602,13 +599,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -666,13 +663,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -730,13 +727,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -794,13 +791,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -858,13 +855,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -922,13 +919,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -986,13 +983,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1050,13 +1047,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1114,13 +1111,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1178,13 +1175,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1242,13 +1239,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1306,13 +1303,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1370,13 +1367,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1434,13 +1431,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1498,13 +1495,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1562,13 +1559,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1626,13 +1623,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1690,13 +1687,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1754,13 +1751,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1818,13 +1815,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1882,13 +1879,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1946,13 +1943,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -2010,13 +2007,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -2074,13 +2071,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -2138,13 +2135,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -2202,13 +2199,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -2266,13 +2263,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -2330,13 +2327,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -2394,13 +2391,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -2458,13 +2455,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -2522,13 +2519,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -2586,13 +2583,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -2650,13 +2647,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -2714,13 +2711,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -2778,13 +2775,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -2842,13 +2839,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -2906,13 +2903,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -2970,13 +2967,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -3034,13 +3031,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -3098,13 +3095,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -3162,13 +3159,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="C43" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -3226,13 +3223,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -3290,13 +3287,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="C45" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -3354,13 +3351,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -3418,13 +3415,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -3482,13 +3479,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -3546,13 +3543,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -3610,13 +3607,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -3674,13 +3671,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -3738,13 +3735,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -3802,13 +3799,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -3866,13 +3863,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="C54" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -3930,13 +3927,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -3994,13 +3991,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -4058,13 +4055,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="C57" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -4122,13 +4119,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -4186,13 +4183,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="C59" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -4250,13 +4247,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -4314,13 +4311,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -4378,13 +4375,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -4442,13 +4439,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="C63" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -4506,13 +4503,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -4570,13 +4567,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="C65" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -4634,13 +4631,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -4698,13 +4695,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="C67" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -4762,13 +4759,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="C68" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -4826,13 +4823,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -4890,13 +4887,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -4954,13 +4951,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -5018,13 +5015,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -5082,13 +5079,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="C73" s="3" t="n">
+      <c r="C73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -5146,13 +5143,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -5210,13 +5207,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="C75" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -5274,13 +5271,13 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="C76" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -5338,13 +5335,13 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -5402,13 +5399,13 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -5466,13 +5463,13 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -5530,13 +5527,13 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -5592,13 +5589,13 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -5654,13 +5651,13 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -5716,13 +5713,13 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C83" s="3" t="n">
+      <c r="C83" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -5780,13 +5777,13 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -5844,13 +5841,13 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C85" s="3" t="n">
+      <c r="C85" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -5908,13 +5905,13 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C86" s="3" t="n">
+      <c r="C86" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -5972,13 +5969,13 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C87" s="3" t="n">
+      <c r="C87" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -6036,13 +6033,13 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -6100,13 +6097,13 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="C89" s="3" t="n">
+      <c r="C89" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -6164,13 +6161,13 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="C90" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -6228,13 +6225,13 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="C91" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -6292,13 +6289,13 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="C92" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -6356,13 +6353,13 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -6420,13 +6417,13 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="C94" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -6484,13 +6481,13 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="C95" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="D95" t="inlineStr">
@@ -6548,13 +6545,13 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="C96" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="D96" t="inlineStr">
@@ -6612,13 +6609,13 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="C97" s="3" t="n">
+      <c r="C97" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -6676,13 +6673,13 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="C98" s="3" t="n">
+      <c r="C98" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -6740,13 +6737,13 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="C99" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -6804,13 +6801,13 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="C100" s="3" t="n">
+      <c r="C100" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -6868,13 +6865,13 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="C101" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="D101" t="inlineStr">
@@ -6932,13 +6929,13 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="C102" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="D102" t="inlineStr">
@@ -6996,13 +6993,13 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="C103" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="D103" t="inlineStr">
@@ -7060,13 +7057,13 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="C104" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D104" t="inlineStr">
@@ -7124,13 +7121,13 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="C105" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D105" t="inlineStr">
@@ -7188,13 +7185,13 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="C106" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D106" t="inlineStr">
@@ -7252,13 +7249,13 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="C107" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D107" t="inlineStr">
@@ -7316,13 +7313,13 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="C108" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D108" t="inlineStr">
@@ -7380,13 +7377,13 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="C109" s="3" t="n">
+      <c r="C109" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D109" t="inlineStr">
@@ -7444,13 +7441,13 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="C110" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="D110" t="inlineStr">
@@ -7508,13 +7505,13 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="C111" s="3" t="n">
+      <c r="C111" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="D111" t="inlineStr">
@@ -7572,13 +7569,13 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="C112" s="3" t="n">
+      <c r="C112" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="D112" t="inlineStr">
@@ -7636,13 +7633,13 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="C113" s="3" t="n">
+      <c r="C113" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D113" t="inlineStr">
@@ -7700,13 +7697,13 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="C114" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D114" t="inlineStr">
@@ -7764,13 +7761,13 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="C115" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D115" t="inlineStr">
@@ -7828,13 +7825,13 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="C116" s="3" t="n">
+      <c r="C116" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="D116" t="inlineStr">
@@ -7892,13 +7889,13 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="C117" s="3" t="n">
+      <c r="C117" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="D117" t="inlineStr">
@@ -7956,13 +7953,13 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="C118" s="3" t="n">
+      <c r="C118" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="D118" t="inlineStr">
@@ -8020,13 +8017,13 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="C119" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="D119" t="inlineStr">
@@ -8084,13 +8081,13 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C120" s="3" t="n">
+      <c r="C120" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="D120" t="inlineStr">
@@ -8148,13 +8145,13 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C121" s="3" t="n">
+      <c r="C121" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="D121" t="inlineStr">
@@ -8212,13 +8209,13 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="C122" s="3" t="n">
+      <c r="C122" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="D122" t="inlineStr">
@@ -8276,13 +8273,13 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="C123" s="3" t="n">
+      <c r="C123" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="D123" t="inlineStr">
@@ -8340,13 +8337,13 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="C124" s="3" t="n">
+      <c r="C124" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="D124" t="inlineStr">
@@ -8404,13 +8401,13 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="C125" s="3" t="n">
+      <c r="C125" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="D125" t="inlineStr">
@@ -8468,13 +8465,13 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="C126" s="3" t="n">
+      <c r="C126" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="D126" t="inlineStr">
@@ -8532,13 +8529,13 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="C127" s="3" t="n">
+      <c r="C127" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="D127" t="inlineStr">
@@ -8596,13 +8593,13 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C128" s="3" t="n">
+      <c r="C128" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="D128" t="inlineStr">
@@ -8660,13 +8657,13 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="C129" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="D129" t="inlineStr">
@@ -8724,13 +8721,13 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C130" s="3" t="n">
+      <c r="C130" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="D130" t="inlineStr">
@@ -8788,13 +8785,13 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="C131" s="3" t="n">
+      <c r="C131" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D131" t="inlineStr">
@@ -8852,13 +8849,13 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="C132" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D132" t="inlineStr">
@@ -8916,13 +8913,13 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="C133" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="D133" t="inlineStr">
@@ -8980,13 +8977,13 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="C134" s="3" t="n">
+      <c r="C134" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="D134" t="inlineStr">
@@ -9044,13 +9041,13 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="C135" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="D135" t="inlineStr">
@@ -9108,13 +9105,13 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="C136" s="3" t="n">
+      <c r="C136" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="D136" t="inlineStr">
@@ -9172,13 +9169,13 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="C137" s="3" t="n">
+      <c r="C137" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="D137" t="inlineStr">
@@ -9236,13 +9233,13 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="C138" s="3" t="n">
+      <c r="C138" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="D138" t="inlineStr">
@@ -9300,13 +9297,13 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="C139" s="3" t="n">
+      <c r="C139" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="D139" t="inlineStr">
@@ -9364,13 +9361,13 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="C140" s="3" t="n">
+      <c r="C140" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D140" t="inlineStr">
@@ -9428,13 +9425,13 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="C141" s="3" t="n">
+      <c r="C141" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D141" t="inlineStr">
@@ -9492,13 +9489,13 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="C142" s="3" t="n">
+      <c r="C142" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D142" t="inlineStr">
@@ -9556,13 +9553,13 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="C143" s="3" t="n">
+      <c r="C143" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="D143" t="inlineStr">
@@ -9620,13 +9617,13 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="C144" s="3" t="n">
+      <c r="C144" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="D144" t="inlineStr">
@@ -9684,13 +9681,13 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="C145" s="3" t="n">
+      <c r="C145" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="D145" t="inlineStr">
@@ -9748,13 +9745,13 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="C146" s="3" t="n">
+      <c r="C146" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="D146" t="inlineStr">
@@ -9812,13 +9809,13 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="C147" s="3" t="n">
+      <c r="C147" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="D147" t="inlineStr">
@@ -9876,13 +9873,13 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="C148" s="3" t="n">
+      <c r="C148" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="D148" t="inlineStr">
@@ -9940,13 +9937,13 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="C149" s="3" t="n">
+      <c r="C149" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="D149" t="inlineStr">
@@ -10004,13 +10001,13 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="C150" s="3" t="n">
+      <c r="C150" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="D150" t="inlineStr">
@@ -10068,13 +10065,13 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="C151" s="3" t="n">
+      <c r="C151" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="D151" t="inlineStr">
@@ -10132,13 +10129,13 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="C152" s="3" t="n">
+      <c r="C152" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D152" t="inlineStr">
@@ -10196,13 +10193,13 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="C153" s="3" t="n">
+      <c r="C153" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D153" t="inlineStr">
@@ -10260,13 +10257,13 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="C154" s="3" t="n">
+      <c r="C154" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D154" t="inlineStr">
@@ -10324,13 +10321,13 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="C155" s="3" t="n">
+      <c r="C155" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="D155" t="inlineStr">
@@ -10388,13 +10385,13 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="C156" s="3" t="n">
+      <c r="C156" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="D156" t="inlineStr">
@@ -10452,13 +10449,13 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="C157" s="3" t="n">
+      <c r="C157" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="D157" t="inlineStr">
@@ -10516,13 +10513,13 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="C158" s="3" t="n">
+      <c r="C158" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D158" t="inlineStr">
@@ -10580,13 +10577,13 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="C159" s="3" t="n">
+      <c r="C159" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D159" t="inlineStr">
@@ -10644,13 +10641,13 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="C160" s="3" t="n">
+      <c r="C160" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D160" t="inlineStr">
@@ -10708,13 +10705,13 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="C161" s="3" t="n">
+      <c r="C161" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="D161" t="inlineStr">
@@ -10772,13 +10769,13 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="C162" s="3" t="n">
+      <c r="C162" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="D162" t="inlineStr">
@@ -10836,13 +10833,13 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="C163" s="3" t="n">
+      <c r="C163" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="D163" t="inlineStr">
@@ -10900,13 +10897,13 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="C164" s="3" t="n">
+      <c r="C164" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="D164" t="inlineStr">
@@ -10964,13 +10961,13 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="C165" s="3" t="n">
+      <c r="C165" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="D165" t="inlineStr">
@@ -11028,13 +11025,13 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="C166" s="3" t="n">
+      <c r="C166" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="D166" t="inlineStr">
@@ -11092,13 +11089,13 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="C167" s="3" t="n">
+      <c r="C167" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D167" t="inlineStr">
@@ -11156,13 +11153,13 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="C168" s="3" t="n">
+      <c r="C168" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D168" t="inlineStr">
@@ -11220,13 +11217,13 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="C169" s="3" t="n">
+      <c r="C169" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D169" t="inlineStr">
@@ -11284,13 +11281,13 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" s="1" t="n">
         <v>168</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="C170" s="3" t="n">
+      <c r="C170" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="D170" t="inlineStr">
@@ -11348,13 +11345,13 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" s="1" t="n">
         <v>169</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="C171" s="3" t="n">
+      <c r="C171" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="D171" t="inlineStr">
@@ -11412,13 +11409,13 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" s="1" t="n">
         <v>170</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="C172" s="3" t="n">
+      <c r="C172" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="D172" t="inlineStr">
@@ -11476,13 +11473,13 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173" s="1" t="n">
         <v>171</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="C173" s="3" t="n">
+      <c r="C173" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="D173" t="inlineStr">
@@ -11540,13 +11537,13 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="C174" s="3" t="n">
+      <c r="C174" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="D174" t="inlineStr">
@@ -11604,13 +11601,13 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="C175" s="3" t="n">
+      <c r="C175" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="D175" t="inlineStr">
@@ -11668,13 +11665,13 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176" s="1" t="n">
         <v>174</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="C176" s="3" t="n">
+      <c r="C176" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D176" t="inlineStr">
@@ -11732,13 +11729,13 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177" s="1" t="n">
         <v>175</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="C177" s="3" t="n">
+      <c r="C177" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D177" t="inlineStr">
@@ -11796,13 +11793,13 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178" s="1" t="n">
         <v>176</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="C178" s="3" t="n">
+      <c r="C178" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D178" t="inlineStr">
@@ -11860,13 +11857,13 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179" s="1" t="n">
         <v>177</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="C179" s="3" t="n">
+      <c r="C179" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="D179" t="inlineStr">
@@ -11924,13 +11921,13 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180" s="1" t="n">
         <v>178</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="C180" s="3" t="n">
+      <c r="C180" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="D180" t="inlineStr">
@@ -11988,13 +11985,13 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="C181" s="3" t="n">
+      <c r="C181" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="D181" t="inlineStr">
@@ -12052,13 +12049,13 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182" s="1" t="n">
         <v>180</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="C182" s="3" t="n">
+      <c r="C182" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="D182" t="inlineStr">
@@ -12116,13 +12113,13 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" s="1" t="n">
         <v>181</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="C183" s="3" t="n">
+      <c r="C183" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="D183" t="inlineStr">
@@ -12180,13 +12177,13 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184" s="1" t="n">
         <v>182</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="C184" s="3" t="n">
+      <c r="C184" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="D184" t="inlineStr">
@@ -12244,13 +12241,13 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
+      <c r="A185" s="1" t="n">
         <v>183</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="C185" s="3" t="n">
+      <c r="C185" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="D185" t="inlineStr">
@@ -12308,13 +12305,13 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186" s="1" t="n">
         <v>184</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="C186" s="3" t="n">
+      <c r="C186" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="D186" t="inlineStr">
@@ -12372,13 +12369,13 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187" s="1" t="n">
         <v>185</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="C187" s="3" t="n">
+      <c r="C187" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="D187" t="inlineStr">
@@ -12436,13 +12433,13 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188" s="1" t="n">
         <v>186</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="C188" s="3" t="n">
+      <c r="C188" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="D188" t="inlineStr">
@@ -12500,13 +12497,13 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
+      <c r="A189" s="1" t="n">
         <v>187</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="C189" s="3" t="n">
+      <c r="C189" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="D189" t="inlineStr">
@@ -12564,13 +12561,13 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
+      <c r="A190" s="1" t="n">
         <v>188</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="C190" s="3" t="n">
+      <c r="C190" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="D190" t="inlineStr">
@@ -12628,13 +12625,13 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
+      <c r="A191" s="1" t="n">
         <v>189</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="C191" s="3" t="n">
+      <c r="C191" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="D191" t="inlineStr">
@@ -12692,13 +12689,13 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192" s="1" t="n">
         <v>190</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="C192" s="3" t="n">
+      <c r="C192" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="D192" t="inlineStr">
@@ -12756,13 +12753,13 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193" s="1" t="n">
         <v>191</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="C193" s="3" t="n">
+      <c r="C193" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="D193" t="inlineStr">
@@ -12820,13 +12817,13 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194" s="1" t="n">
         <v>192</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="C194" s="3" t="n">
+      <c r="C194" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D194" t="inlineStr">
@@ -12884,13 +12881,13 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
+      <c r="A195" s="1" t="n">
         <v>193</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="C195" s="3" t="n">
+      <c r="C195" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D195" t="inlineStr">
@@ -12948,13 +12945,13 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
+      <c r="A196" s="1" t="n">
         <v>194</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="C196" s="3" t="n">
+      <c r="C196" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D196" t="inlineStr">
@@ -13012,13 +13009,13 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
+      <c r="A197" s="1" t="n">
         <v>195</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="C197" s="3" t="n">
+      <c r="C197" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="D197" t="inlineStr">
@@ -13074,13 +13071,13 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198" s="1" t="n">
         <v>196</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="C198" s="3" t="n">
+      <c r="C198" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="D198" t="inlineStr">
@@ -13136,13 +13133,13 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
+      <c r="A199" s="1" t="n">
         <v>197</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="C199" s="3" t="n">
+      <c r="C199" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="D199" t="inlineStr">
@@ -13198,13 +13195,13 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
+      <c r="A200" s="1" t="n">
         <v>198</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="C200" s="3" t="n">
+      <c r="C200" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="D200" t="inlineStr">
@@ -13262,13 +13259,13 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201" s="1" t="n">
         <v>199</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="C201" s="3" t="n">
+      <c r="C201" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="D201" t="inlineStr">
@@ -13326,13 +13323,13 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="1" t="n">
         <v>200</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="C202" s="3" t="n">
+      <c r="C202" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="D202" t="inlineStr">
@@ -13390,13 +13387,13 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="1" t="n">
         <v>201</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="C203" s="3" t="n">
+      <c r="C203" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D203" t="inlineStr">
@@ -13450,13 +13447,13 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204" s="1" t="n">
         <v>202</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="C204" s="3" t="n">
+      <c r="C204" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D204" t="inlineStr">
@@ -13510,13 +13507,13 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="1" t="n">
         <v>203</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="C205" s="3" t="n">
+      <c r="C205" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D205" t="inlineStr">
@@ -13570,13 +13567,13 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="1" t="n">
         <v>204</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="C206" s="3" t="n">
+      <c r="C206" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="D206" t="inlineStr">
@@ -13634,13 +13631,13 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="1" t="n">
         <v>205</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="C207" s="3" t="n">
+      <c r="C207" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="D207" t="inlineStr">
@@ -13698,13 +13695,13 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="1" t="n">
         <v>206</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="C208" s="3" t="n">
+      <c r="C208" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="D208" t="inlineStr">
@@ -13762,13 +13759,13 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="1" t="n">
         <v>207</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="C209" s="3" t="n">
+      <c r="C209" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="D209" t="inlineStr">
@@ -13824,13 +13821,13 @@
       <c r="T209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="1" t="n">
         <v>208</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="C210" s="3" t="n">
+      <c r="C210" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="D210" t="inlineStr">
@@ -13886,13 +13883,13 @@
       <c r="T210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="1" t="n">
         <v>209</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="C211" s="3" t="n">
+      <c r="C211" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="D211" t="inlineStr">
@@ -13948,13 +13945,13 @@
       <c r="T211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="1" t="n">
         <v>210</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="C212" s="3" t="n">
+      <c r="C212" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="D212" t="inlineStr">
@@ -14012,13 +14009,13 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="1" t="n">
         <v>211</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="C213" s="3" t="n">
+      <c r="C213" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="D213" t="inlineStr">
@@ -14076,13 +14073,13 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="1" t="n">
         <v>212</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="C214" s="3" t="n">
+      <c r="C214" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="D214" t="inlineStr">
@@ -14140,13 +14137,13 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215" s="1" t="n">
         <v>213</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="C215" s="3" t="n">
+      <c r="C215" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="D215" t="inlineStr">
@@ -14204,13 +14201,13 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216" s="1" t="n">
         <v>214</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="C216" s="3" t="n">
+      <c r="C216" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="D216" t="inlineStr">
@@ -14268,13 +14265,13 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217" s="1" t="n">
         <v>215</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="C217" s="3" t="n">
+      <c r="C217" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="D217" t="inlineStr">
@@ -14332,13 +14329,13 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218" s="1" t="n">
         <v>216</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="C218" s="3" t="n">
+      <c r="C218" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="D218" t="inlineStr">
@@ -14396,13 +14393,13 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219" s="1" t="n">
         <v>217</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="C219" s="3" t="n">
+      <c r="C219" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="D219" t="inlineStr">
@@ -14460,13 +14457,13 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220" s="1" t="n">
         <v>218</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="C220" s="3" t="n">
+      <c r="C220" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="D220" t="inlineStr">
@@ -14524,13 +14521,13 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221" s="1" t="n">
         <v>219</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="C221" s="3" t="n">
+      <c r="C221" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="D221" t="inlineStr">
@@ -14588,13 +14585,13 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222" s="1" t="n">
         <v>220</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="C222" s="3" t="n">
+      <c r="C222" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="D222" t="inlineStr">
@@ -14652,13 +14649,13 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223" s="1" t="n">
         <v>221</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="C223" s="3" t="n">
+      <c r="C223" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="D223" t="inlineStr">
@@ -14716,13 +14713,13 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224" s="1" t="n">
         <v>222</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="C224" s="3" t="n">
+      <c r="C224" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="D224" t="inlineStr">
@@ -14778,13 +14775,13 @@
       <c r="T224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225" s="1" t="n">
         <v>223</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="C225" s="3" t="n">
+      <c r="C225" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="D225" t="inlineStr">
@@ -14840,13 +14837,13 @@
       <c r="T225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226" s="1" t="n">
         <v>224</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="C226" s="3" t="n">
+      <c r="C226" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="D226" t="inlineStr">
@@ -14902,13 +14899,13 @@
       <c r="T226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="1" t="n">
         <v>225</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="C227" s="3" t="n">
+      <c r="C227" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="D227" t="inlineStr">
@@ -14966,13 +14963,13 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228" s="1" t="n">
         <v>226</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="C228" s="3" t="n">
+      <c r="C228" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="D228" t="inlineStr">
@@ -15030,13 +15027,13 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229" s="1" t="n">
         <v>227</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="C229" s="3" t="n">
+      <c r="C229" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="D229" t="inlineStr">
@@ -15094,13 +15091,13 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230" s="1" t="n">
         <v>228</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="C230" s="3" t="n">
+      <c r="C230" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D230" t="inlineStr">
@@ -15158,13 +15155,13 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231" s="1" t="n">
         <v>229</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="C231" s="3" t="n">
+      <c r="C231" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D231" t="inlineStr">
@@ -15222,13 +15219,13 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232" s="1" t="n">
         <v>230</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="C232" s="3" t="n">
+      <c r="C232" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D232" t="inlineStr">
@@ -15286,13 +15283,13 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233" s="1" t="n">
         <v>231</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="C233" s="3" t="n">
+      <c r="C233" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="D233" t="inlineStr">
@@ -15350,13 +15347,13 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="1" t="n">
         <v>232</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="C234" s="3" t="n">
+      <c r="C234" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="D234" t="inlineStr">
@@ -15414,13 +15411,13 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" s="1" t="n">
         <v>233</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="C235" s="3" t="n">
+      <c r="C235" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="D235" t="inlineStr">
@@ -15478,13 +15475,13 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236" s="1" t="n">
         <v>234</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="C236" s="3" t="n">
+      <c r="C236" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="D236" t="inlineStr">
@@ -15540,13 +15537,13 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237" s="1" t="n">
         <v>235</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="C237" s="3" t="n">
+      <c r="C237" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="D237" t="inlineStr">
@@ -15602,13 +15599,13 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238" s="1" t="n">
         <v>236</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="C238" s="3" t="n">
+      <c r="C238" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="D238" t="inlineStr">
@@ -15664,13 +15661,13 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239" s="1" t="n">
         <v>237</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="C239" s="3" t="n">
+      <c r="C239" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="D239" t="inlineStr">
@@ -15728,13 +15725,13 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240" s="1" t="n">
         <v>238</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="C240" s="3" t="n">
+      <c r="C240" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="D240" t="inlineStr">
@@ -15792,13 +15789,13 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241" s="1" t="n">
         <v>239</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="C241" s="3" t="n">
+      <c r="C241" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="D241" t="inlineStr">
@@ -15856,13 +15853,13 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242" s="1" t="n">
         <v>240</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="C242" s="3" t="n">
+      <c r="C242" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="D242" t="inlineStr">
@@ -15920,13 +15917,13 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243" s="1" t="n">
         <v>241</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="C243" s="3" t="n">
+      <c r="C243" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="D243" t="inlineStr">
@@ -15984,13 +15981,13 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244" s="1" t="n">
         <v>242</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="C244" s="3" t="n">
+      <c r="C244" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="D244" t="inlineStr">
@@ -16048,13 +16045,13 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245" s="1" t="n">
         <v>243</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="C245" s="3" t="n">
+      <c r="C245" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="D245" t="inlineStr">
@@ -16110,13 +16107,13 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246" s="1" t="n">
         <v>244</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="C246" s="3" t="n">
+      <c r="C246" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="D246" t="inlineStr">
@@ -16172,13 +16169,13 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247" s="1" t="n">
         <v>245</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="C247" s="3" t="n">
+      <c r="C247" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="D247" t="inlineStr">
@@ -16234,13 +16231,13 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248" s="1" t="n">
         <v>246</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="C248" s="3" t="n">
+      <c r="C248" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="D248" t="inlineStr">
@@ -16298,13 +16295,13 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249" s="1" t="n">
         <v>247</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="C249" s="3" t="n">
+      <c r="C249" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="D249" t="inlineStr">
@@ -16362,13 +16359,13 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250" s="1" t="n">
         <v>248</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="C250" s="3" t="n">
+      <c r="C250" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="D250" t="inlineStr">
@@ -16426,13 +16423,13 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251" s="1" t="n">
         <v>249</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="C251" s="3" t="n">
+      <c r="C251" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="D251" t="inlineStr">
@@ -16490,13 +16487,13 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252" s="1" t="n">
         <v>250</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="C252" s="3" t="n">
+      <c r="C252" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="D252" t="inlineStr">
@@ -16554,13 +16551,13 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253" s="1" t="n">
         <v>251</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="C253" s="3" t="n">
+      <c r="C253" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="D253" t="inlineStr">
@@ -16618,13 +16615,13 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254" s="1" t="n">
         <v>252</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="C254" s="3" t="n">
+      <c r="C254" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="D254" t="inlineStr">
@@ -16682,13 +16679,13 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255" s="1" t="n">
         <v>253</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="C255" s="3" t="n">
+      <c r="C255" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="D255" t="inlineStr">
@@ -16746,13 +16743,13 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256" s="1" t="n">
         <v>254</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="C256" s="3" t="n">
+      <c r="C256" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="D256" t="inlineStr">
@@ -16810,13 +16807,13 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257" s="1" t="n">
         <v>255</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="C257" s="3" t="n">
+      <c r="C257" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="D257" t="inlineStr">
@@ -16874,13 +16871,13 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
+      <c r="A258" s="1" t="n">
         <v>256</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="C258" s="3" t="n">
+      <c r="C258" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="D258" t="inlineStr">
@@ -16938,13 +16935,13 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
+      <c r="A259" s="1" t="n">
         <v>257</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="C259" s="3" t="n">
+      <c r="C259" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="D259" t="inlineStr">
@@ -17002,13 +16999,13 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
+      <c r="A260" s="1" t="n">
         <v>258</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="C260" s="3" t="n">
+      <c r="C260" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="D260" t="inlineStr">
@@ -17064,13 +17061,13 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
+      <c r="A261" s="1" t="n">
         <v>259</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="C261" s="3" t="n">
+      <c r="C261" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="D261" t="inlineStr">
@@ -17126,13 +17123,13 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
+      <c r="A262" s="1" t="n">
         <v>260</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="C262" s="3" t="n">
+      <c r="C262" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="D262" t="inlineStr">
@@ -17188,13 +17185,13 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263" s="1" t="n">
         <v>261</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C263" s="3" t="n">
+      <c r="C263" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="D263" t="inlineStr">
@@ -17252,13 +17249,13 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
+      <c r="A264" s="1" t="n">
         <v>262</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C264" s="3" t="n">
+      <c r="C264" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="D264" t="inlineStr">
@@ -17316,13 +17313,13 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
+      <c r="A265" s="1" t="n">
         <v>263</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C265" s="3" t="n">
+      <c r="C265" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="D265" t="inlineStr">
@@ -17380,13 +17377,13 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
+      <c r="A266" s="1" t="n">
         <v>264</v>
       </c>
       <c r="B266" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C266" s="3" t="n">
+      <c r="C266" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="D266" t="inlineStr">
@@ -17440,13 +17437,13 @@
       <c r="T266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267" s="1" t="n">
         <v>265</v>
       </c>
       <c r="B267" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C267" s="3" t="n">
+      <c r="C267" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="D267" t="inlineStr">
@@ -17500,13 +17497,13 @@
       <c r="T267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="n">
+      <c r="A268" s="1" t="n">
         <v>266</v>
       </c>
       <c r="B268" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C268" s="3" t="n">
+      <c r="C268" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="D268" t="inlineStr">
@@ -17560,13 +17557,13 @@
       <c r="T268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" t="n">
+      <c r="A269" s="1" t="n">
         <v>267</v>
       </c>
       <c r="B269" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="C269" s="3" t="n">
+      <c r="C269" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="D269" t="inlineStr">
@@ -17622,13 +17619,13 @@
       <c r="T269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" t="n">
+      <c r="A270" s="1" t="n">
         <v>268</v>
       </c>
       <c r="B270" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="C270" s="3" t="n">
+      <c r="C270" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="D270" t="inlineStr">
@@ -17684,13 +17681,13 @@
       <c r="T270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271" s="1" t="n">
         <v>269</v>
       </c>
       <c r="B271" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="C271" s="3" t="n">
+      <c r="C271" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="D271" t="inlineStr">
@@ -17746,13 +17743,13 @@
       <c r="T271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272" s="1" t="n">
         <v>270</v>
       </c>
       <c r="B272" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C272" s="3" t="n">
+      <c r="C272" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="D272" t="inlineStr">
@@ -17806,13 +17803,13 @@
       <c r="T272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273" s="1" t="n">
         <v>271</v>
       </c>
       <c r="B273" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C273" s="3" t="n">
+      <c r="C273" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="D273" t="inlineStr">
@@ -17866,13 +17863,13 @@
       <c r="T273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274" s="1" t="n">
         <v>272</v>
       </c>
       <c r="B274" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C274" s="3" t="n">
+      <c r="C274" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="D274" t="inlineStr">
@@ -17926,13 +17923,13 @@
       <c r="T274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" t="n">
+      <c r="A275" s="1" t="n">
         <v>273</v>
       </c>
       <c r="B275" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="C275" s="3" t="n">
+      <c r="C275" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D275" t="inlineStr">
@@ -17986,13 +17983,13 @@
       <c r="T275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276" s="1" t="n">
         <v>274</v>
       </c>
       <c r="B276" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="C276" s="3" t="n">
+      <c r="C276" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D276" t="inlineStr">
@@ -18046,13 +18043,13 @@
       <c r="T276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" t="n">
+      <c r="A277" s="1" t="n">
         <v>275</v>
       </c>
       <c r="B277" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="C277" s="3" t="n">
+      <c r="C277" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D277" t="inlineStr">
@@ -18106,13 +18103,13 @@
       <c r="T277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" t="n">
+      <c r="A278" s="1" t="n">
         <v>276</v>
       </c>
       <c r="B278" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="C278" s="3" t="n">
+      <c r="C278" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D278" t="inlineStr">
@@ -18166,13 +18163,13 @@
       <c r="T278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279" s="1" t="n">
         <v>277</v>
       </c>
       <c r="B279" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="C279" s="3" t="n">
+      <c r="C279" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D279" t="inlineStr">
@@ -18226,13 +18223,13 @@
       <c r="T279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280" s="1" t="n">
         <v>278</v>
       </c>
       <c r="B280" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="C280" s="3" t="n">
+      <c r="C280" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D280" t="inlineStr">
@@ -18286,13 +18283,13 @@
       <c r="T280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281" s="1" t="n">
         <v>279</v>
       </c>
       <c r="B281" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="C281" s="3" t="n">
+      <c r="C281" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="D281" t="inlineStr">
@@ -18346,13 +18343,13 @@
       <c r="T281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282" s="1" t="n">
         <v>280</v>
       </c>
       <c r="B282" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="C282" s="3" t="n">
+      <c r="C282" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="D282" t="inlineStr">
@@ -18406,13 +18403,13 @@
       <c r="T282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283" s="1" t="n">
         <v>281</v>
       </c>
       <c r="B283" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="C283" s="3" t="n">
+      <c r="C283" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="D283" t="inlineStr">
@@ -18466,13 +18463,13 @@
       <c r="T283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284" s="1" t="n">
         <v>282</v>
       </c>
       <c r="B284" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="C284" s="3" t="n">
+      <c r="C284" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D284" t="inlineStr">
@@ -18526,13 +18523,13 @@
       <c r="T284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285" s="1" t="n">
         <v>283</v>
       </c>
       <c r="B285" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="C285" s="3" t="n">
+      <c r="C285" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D285" t="inlineStr">
@@ -18586,13 +18583,13 @@
       <c r="T285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="1" t="n">
         <v>284</v>
       </c>
       <c r="B286" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="C286" s="3" t="n">
+      <c r="C286" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D286" t="inlineStr">
@@ -18646,13 +18643,13 @@
       <c r="T286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287" s="1" t="n">
         <v>285</v>
       </c>
       <c r="B287" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="C287" s="3" t="n">
+      <c r="C287" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="D287" t="inlineStr">
@@ -18706,13 +18703,13 @@
       <c r="T287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288" s="1" t="n">
         <v>286</v>
       </c>
       <c r="B288" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="C288" s="3" t="n">
+      <c r="C288" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="D288" t="inlineStr">
@@ -18766,13 +18763,13 @@
       <c r="T288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" t="n">
+      <c r="A289" s="1" t="n">
         <v>287</v>
       </c>
       <c r="B289" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="C289" s="3" t="n">
+      <c r="C289" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="D289" t="inlineStr">
@@ -18826,13 +18823,13 @@
       <c r="T289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" t="n">
+      <c r="A290" s="1" t="n">
         <v>288</v>
       </c>
       <c r="B290" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="C290" s="3" t="n">
+      <c r="C290" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="D290" t="inlineStr">
@@ -18886,13 +18883,13 @@
       <c r="T290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" t="n">
+      <c r="A291" s="1" t="n">
         <v>289</v>
       </c>
       <c r="B291" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="C291" s="3" t="n">
+      <c r="C291" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="D291" t="inlineStr">
@@ -18946,13 +18943,13 @@
       <c r="T291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" t="n">
+      <c r="A292" s="1" t="n">
         <v>290</v>
       </c>
       <c r="B292" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="C292" s="3" t="n">
+      <c r="C292" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="D292" t="inlineStr">
@@ -19006,13 +19003,13 @@
       <c r="T292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" t="n">
+      <c r="A293" s="1" t="n">
         <v>291</v>
       </c>
       <c r="B293" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="C293" s="3" t="n">
+      <c r="C293" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="D293" t="inlineStr">
@@ -19068,13 +19065,13 @@
       <c r="T293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" t="n">
+      <c r="A294" s="1" t="n">
         <v>292</v>
       </c>
       <c r="B294" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="C294" s="3" t="n">
+      <c r="C294" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="D294" t="inlineStr">
@@ -19130,13 +19127,13 @@
       <c r="T294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" t="n">
+      <c r="A295" s="1" t="n">
         <v>293</v>
       </c>
       <c r="B295" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="C295" s="3" t="n">
+      <c r="C295" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="D295" t="inlineStr">
@@ -19192,13 +19189,13 @@
       <c r="T295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296" s="1" t="n">
         <v>294</v>
       </c>
       <c r="B296" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="C296" s="3" t="n">
+      <c r="C296" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D296" t="inlineStr">
@@ -19254,13 +19251,13 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
+      <c r="A297" s="1" t="n">
         <v>295</v>
       </c>
       <c r="B297" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="C297" s="3" t="n">
+      <c r="C297" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D297" t="inlineStr">
@@ -19316,13 +19313,13 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
+      <c r="A298" s="1" t="n">
         <v>296</v>
       </c>
       <c r="B298" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="C298" s="3" t="n">
+      <c r="C298" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D298" t="inlineStr">
@@ -19378,13 +19375,13 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
+      <c r="A299" s="1" t="n">
         <v>297</v>
       </c>
       <c r="B299" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C299" s="3" t="n">
+      <c r="C299" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="D299" t="inlineStr">
@@ -19442,13 +19439,13 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
+      <c r="A300" s="1" t="n">
         <v>298</v>
       </c>
       <c r="B300" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C300" s="3" t="n">
+      <c r="C300" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="D300" t="inlineStr">
@@ -19506,13 +19503,13 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
+      <c r="A301" s="1" t="n">
         <v>299</v>
       </c>
       <c r="B301" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="C301" s="3" t="n">
+      <c r="C301" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="D301" t="inlineStr">
@@ -19570,13 +19567,13 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="n">
+      <c r="A302" s="1" t="n">
         <v>300</v>
       </c>
       <c r="B302" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="C302" s="3" t="n">
+      <c r="C302" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D302" t="inlineStr">
@@ -19634,13 +19631,13 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="n">
+      <c r="A303" s="1" t="n">
         <v>301</v>
       </c>
       <c r="B303" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="C303" s="3" t="n">
+      <c r="C303" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D303" t="inlineStr">
@@ -19698,13 +19695,13 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="n">
+      <c r="A304" s="1" t="n">
         <v>302</v>
       </c>
       <c r="B304" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="C304" s="3" t="n">
+      <c r="C304" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D304" t="inlineStr">
@@ -19762,13 +19759,13 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="n">
+      <c r="A305" s="1" t="n">
         <v>303</v>
       </c>
       <c r="B305" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="C305" s="3" t="n">
+      <c r="C305" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D305" t="inlineStr">
@@ -19820,13 +19817,13 @@
       <c r="T305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" t="n">
+      <c r="A306" s="1" t="n">
         <v>304</v>
       </c>
       <c r="B306" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="C306" s="3" t="n">
+      <c r="C306" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D306" t="inlineStr">
@@ -19878,13 +19875,13 @@
       <c r="T306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" t="n">
+      <c r="A307" s="1" t="n">
         <v>305</v>
       </c>
       <c r="B307" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="C307" s="3" t="n">
+      <c r="C307" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D307" t="inlineStr">
@@ -19936,13 +19933,13 @@
       <c r="T307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" t="n">
+      <c r="A308" s="1" t="n">
         <v>306</v>
       </c>
       <c r="B308" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C308" s="3" t="n">
+      <c r="C308" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="D308" t="inlineStr">
@@ -19996,13 +19993,13 @@
       <c r="T308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" t="n">
+      <c r="A309" s="1" t="n">
         <v>307</v>
       </c>
       <c r="B309" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C309" s="3" t="n">
+      <c r="C309" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="D309" t="inlineStr">
@@ -20056,13 +20053,13 @@
       <c r="T309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" t="n">
+      <c r="A310" s="1" t="n">
         <v>308</v>
       </c>
       <c r="B310" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="C310" s="3" t="n">
+      <c r="C310" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="D310" t="inlineStr">
@@ -20116,13 +20113,13 @@
       <c r="T310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" t="n">
+      <c r="A311" s="1" t="n">
         <v>309</v>
       </c>
       <c r="B311" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="C311" s="3" t="n">
+      <c r="C311" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D311" t="inlineStr">
@@ -20176,13 +20173,13 @@
       <c r="T311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" t="n">
+      <c r="A312" s="1" t="n">
         <v>310</v>
       </c>
       <c r="B312" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="C312" s="3" t="n">
+      <c r="C312" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D312" t="inlineStr">
@@ -20236,13 +20233,13 @@
       <c r="T312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" t="n">
+      <c r="A313" s="1" t="n">
         <v>311</v>
       </c>
       <c r="B313" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="C313" s="3" t="n">
+      <c r="C313" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D313" t="inlineStr">
@@ -20296,13 +20293,13 @@
       <c r="T313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" t="n">
+      <c r="A314" s="1" t="n">
         <v>312</v>
       </c>
       <c r="B314" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="C314" s="3" t="n">
+      <c r="C314" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="D314" t="inlineStr">
@@ -20348,13 +20345,13 @@
       <c r="T314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" t="n">
+      <c r="A315" s="1" t="n">
         <v>313</v>
       </c>
       <c r="B315" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="C315" s="3" t="n">
+      <c r="C315" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="D315" t="inlineStr">
@@ -20400,13 +20397,13 @@
       <c r="T315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" t="n">
+      <c r="A316" s="1" t="n">
         <v>314</v>
       </c>
       <c r="B316" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="C316" s="3" t="n">
+      <c r="C316" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="D316" t="inlineStr">
@@ -20452,13 +20449,13 @@
       <c r="T316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" t="n">
+      <c r="A317" s="1" t="n">
         <v>315</v>
       </c>
       <c r="B317" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C317" s="3" t="n">
+      <c r="C317" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="D317" t="inlineStr">
@@ -20498,13 +20495,13 @@
       <c r="T317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" t="n">
+      <c r="A318" s="1" t="n">
         <v>316</v>
       </c>
       <c r="B318" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C318" s="3" t="n">
+      <c r="C318" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="D318" t="inlineStr">
@@ -20544,13 +20541,13 @@
       <c r="T318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" t="n">
+      <c r="A319" s="1" t="n">
         <v>317</v>
       </c>
       <c r="B319" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C319" s="3" t="n">
+      <c r="C319" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="D319" t="inlineStr">
@@ -20590,13 +20587,13 @@
       <c r="T319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" t="n">
+      <c r="A320" s="1" t="n">
         <v>318</v>
       </c>
       <c r="B320" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="C320" s="3" t="n">
+      <c r="C320" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D320" t="inlineStr">
@@ -20650,13 +20647,13 @@
       <c r="T320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" t="n">
+      <c r="A321" s="1" t="n">
         <v>319</v>
       </c>
       <c r="B321" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="C321" s="3" t="n">
+      <c r="C321" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D321" t="inlineStr">
@@ -20710,13 +20707,13 @@
       <c r="T321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" t="n">
+      <c r="A322" s="1" t="n">
         <v>320</v>
       </c>
       <c r="B322" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="C322" s="3" t="n">
+      <c r="C322" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D322" t="inlineStr">
@@ -20770,13 +20767,13 @@
       <c r="T322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" t="n">
+      <c r="A323" s="1" t="n">
         <v>321</v>
       </c>
       <c r="B323" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="C323" s="3" t="n">
+      <c r="C323" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="D323" t="inlineStr">
@@ -20828,13 +20825,13 @@
       <c r="T323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" t="n">
+      <c r="A324" s="1" t="n">
         <v>322</v>
       </c>
       <c r="B324" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="C324" s="3" t="n">
+      <c r="C324" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="D324" t="inlineStr">
@@ -20886,13 +20883,13 @@
       <c r="T324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" t="n">
+      <c r="A325" s="1" t="n">
         <v>323</v>
       </c>
       <c r="B325" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="C325" s="3" t="n">
+      <c r="C325" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="D325" t="inlineStr">
@@ -20944,13 +20941,13 @@
       <c r="T325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" t="n">
+      <c r="A326" s="1" t="n">
         <v>324</v>
       </c>
       <c r="B326" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="C326" s="3" t="n">
+      <c r="C326" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="D326" t="inlineStr">
@@ -21006,13 +21003,13 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="n">
+      <c r="A327" s="1" t="n">
         <v>325</v>
       </c>
       <c r="B327" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="C327" s="3" t="n">
+      <c r="C327" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="D327" t="inlineStr">
@@ -21068,13 +21065,13 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
+      <c r="A328" s="1" t="n">
         <v>326</v>
       </c>
       <c r="B328" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="C328" s="3" t="n">
+      <c r="C328" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="D328" t="inlineStr">
@@ -21130,13 +21127,13 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
+      <c r="A329" s="1" t="n">
         <v>327</v>
       </c>
       <c r="B329" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="C329" s="3" t="n">
+      <c r="C329" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D329" t="inlineStr">
@@ -21194,13 +21191,13 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
+      <c r="A330" s="1" t="n">
         <v>328</v>
       </c>
       <c r="B330" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="C330" s="3" t="n">
+      <c r="C330" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D330" t="inlineStr">
@@ -21258,13 +21255,13 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
+      <c r="A331" s="1" t="n">
         <v>329</v>
       </c>
       <c r="B331" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="C331" s="3" t="n">
+      <c r="C331" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D331" t="inlineStr">
@@ -21322,13 +21319,13 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
+      <c r="A332" s="1" t="n">
         <v>330</v>
       </c>
       <c r="B332" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="C332" s="3" t="n">
+      <c r="C332" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D332" t="inlineStr">
@@ -21382,13 +21379,13 @@
       <c r="T332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" t="n">
+      <c r="A333" s="1" t="n">
         <v>331</v>
       </c>
       <c r="B333" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="C333" s="3" t="n">
+      <c r="C333" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D333" t="inlineStr">
@@ -21442,13 +21439,13 @@
       <c r="T333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" t="n">
+      <c r="A334" s="1" t="n">
         <v>332</v>
       </c>
       <c r="B334" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="C334" s="3" t="n">
+      <c r="C334" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D334" t="inlineStr">
@@ -21502,13 +21499,13 @@
       <c r="T334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" t="n">
+      <c r="A335" s="1" t="n">
         <v>333</v>
       </c>
       <c r="B335" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C335" s="3" t="n">
+      <c r="C335" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="D335" t="inlineStr">
@@ -21566,13 +21563,13 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
+      <c r="A336" s="1" t="n">
         <v>334</v>
       </c>
       <c r="B336" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C336" s="3" t="n">
+      <c r="C336" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="D336" t="inlineStr">
@@ -21630,13 +21627,13 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
+      <c r="A337" s="1" t="n">
         <v>335</v>
       </c>
       <c r="B337" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="C337" s="3" t="n">
+      <c r="C337" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="D337" t="inlineStr">
@@ -21694,13 +21691,13 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
+      <c r="A338" s="1" t="n">
         <v>336</v>
       </c>
       <c r="B338" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="C338" s="3" t="n">
+      <c r="C338" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D338" t="inlineStr">
@@ -21756,13 +21753,13 @@
       <c r="T338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" t="n">
+      <c r="A339" s="1" t="n">
         <v>337</v>
       </c>
       <c r="B339" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="C339" s="3" t="n">
+      <c r="C339" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D339" t="inlineStr">
@@ -21818,13 +21815,13 @@
       <c r="T339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" t="n">
+      <c r="A340" s="1" t="n">
         <v>338</v>
       </c>
       <c r="B340" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="C340" s="3" t="n">
+      <c r="C340" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D340" t="inlineStr">
@@ -21880,13 +21877,13 @@
       <c r="T340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" t="n">
+      <c r="A341" s="1" t="n">
         <v>339</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="C341" s="3" t="n">
+      <c r="C341" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="D341" t="inlineStr">
@@ -21940,13 +21937,13 @@
       <c r="T341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" t="n">
+      <c r="A342" s="1" t="n">
         <v>340</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="C342" s="3" t="n">
+      <c r="C342" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="D342" t="inlineStr">
@@ -22000,13 +21997,13 @@
       <c r="T342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" t="n">
+      <c r="A343" s="1" t="n">
         <v>341</v>
       </c>
       <c r="B343" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="C343" s="3" t="n">
+      <c r="C343" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="D343" t="inlineStr">
@@ -22060,13 +22057,13 @@
       <c r="T343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" t="n">
+      <c r="A344" s="1" t="n">
         <v>342</v>
       </c>
       <c r="B344" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C344" s="3" t="n">
+      <c r="C344" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="D344" t="inlineStr">
@@ -22120,13 +22117,13 @@
       <c r="T344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" t="n">
+      <c r="A345" s="1" t="n">
         <v>343</v>
       </c>
       <c r="B345" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C345" s="3" t="n">
+      <c r="C345" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="D345" t="inlineStr">
@@ -22180,13 +22177,13 @@
       <c r="T345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" t="n">
+      <c r="A346" s="1" t="n">
         <v>344</v>
       </c>
       <c r="B346" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="C346" s="3" t="n">
+      <c r="C346" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="D346" t="inlineStr">
@@ -22240,13 +22237,13 @@
       <c r="T346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" t="n">
+      <c r="A347" s="1" t="n">
         <v>345</v>
       </c>
       <c r="B347" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="C347" s="3" t="n">
+      <c r="C347" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D347" t="inlineStr">
@@ -22298,13 +22295,13 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="n">
+      <c r="A348" s="1" t="n">
         <v>346</v>
       </c>
       <c r="B348" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="C348" s="3" t="n">
+      <c r="C348" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D348" t="inlineStr">
@@ -22356,13 +22353,13 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="n">
+      <c r="A349" s="1" t="n">
         <v>347</v>
       </c>
       <c r="B349" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="C349" s="3" t="n">
+      <c r="C349" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D349" t="inlineStr">
@@ -22414,13 +22411,13 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="n">
+      <c r="A350" s="1" t="n">
         <v>348</v>
       </c>
       <c r="B350" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="C350" s="3" t="n">
+      <c r="C350" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="D350" t="inlineStr">
@@ -22472,13 +22469,13 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="n">
+      <c r="A351" s="1" t="n">
         <v>349</v>
       </c>
       <c r="B351" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="C351" s="3" t="n">
+      <c r="C351" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="D351" t="inlineStr">
@@ -22530,13 +22527,13 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="n">
+      <c r="A352" s="1" t="n">
         <v>350</v>
       </c>
       <c r="B352" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="C352" s="3" t="n">
+      <c r="C352" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="D352" t="inlineStr">
@@ -22588,13 +22585,13 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="n">
+      <c r="A353" s="1" t="n">
         <v>351</v>
       </c>
       <c r="B353" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="C353" s="3" t="n">
+      <c r="C353" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="D353" t="inlineStr">
@@ -22648,13 +22645,13 @@
       <c r="T353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" t="n">
+      <c r="A354" s="1" t="n">
         <v>352</v>
       </c>
       <c r="B354" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="C354" s="3" t="n">
+      <c r="C354" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="D354" t="inlineStr">
@@ -22708,13 +22705,13 @@
       <c r="T354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" t="n">
+      <c r="A355" s="1" t="n">
         <v>353</v>
       </c>
       <c r="B355" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="C355" s="3" t="n">
+      <c r="C355" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="D355" t="inlineStr">
@@ -22768,13 +22765,13 @@
       <c r="T355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" t="n">
+      <c r="A356" s="1" t="n">
         <v>354</v>
       </c>
       <c r="B356" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="C356" s="3" t="n">
+      <c r="C356" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D356" t="inlineStr">
@@ -22828,13 +22825,13 @@
       <c r="T356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" t="n">
+      <c r="A357" s="1" t="n">
         <v>355</v>
       </c>
       <c r="B357" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="C357" s="3" t="n">
+      <c r="C357" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D357" t="inlineStr">
@@ -22888,13 +22885,13 @@
       <c r="T357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" t="n">
+      <c r="A358" s="1" t="n">
         <v>356</v>
       </c>
       <c r="B358" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="C358" s="3" t="n">
+      <c r="C358" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D358" t="inlineStr">
@@ -22948,13 +22945,13 @@
       <c r="T358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" t="n">
+      <c r="A359" s="1" t="n">
         <v>357</v>
       </c>
       <c r="B359" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="C359" s="3" t="n">
+      <c r="C359" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="D359" t="inlineStr">
@@ -23002,13 +22999,13 @@
       <c r="T359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" t="n">
+      <c r="A360" s="1" t="n">
         <v>358</v>
       </c>
       <c r="B360" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="C360" s="3" t="n">
+      <c r="C360" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="D360" t="inlineStr">
@@ -23058,13 +23055,13 @@
       <c r="T360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" t="n">
+      <c r="A361" s="1" t="n">
         <v>359</v>
       </c>
       <c r="B361" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="C361" s="3" t="n">
+      <c r="C361" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="D361" t="inlineStr">
@@ -23114,13 +23111,13 @@
       <c r="T361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" t="n">
+      <c r="A362" s="1" t="n">
         <v>360</v>
       </c>
       <c r="B362" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="C362" s="3" t="n">
+      <c r="C362" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="D362" t="inlineStr">
@@ -23176,13 +23173,13 @@
       <c r="T362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" t="n">
+      <c r="A363" s="1" t="n">
         <v>361</v>
       </c>
       <c r="B363" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="C363" s="3" t="n">
+      <c r="C363" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="D363" t="inlineStr">
@@ -23238,13 +23235,13 @@
       <c r="T363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" t="n">
+      <c r="A364" s="1" t="n">
         <v>362</v>
       </c>
       <c r="B364" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="C364" s="3" t="n">
+      <c r="C364" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="D364" t="inlineStr">
@@ -23300,13 +23297,13 @@
       <c r="T364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" t="n">
+      <c r="A365" s="1" t="n">
         <v>363</v>
       </c>
       <c r="B365" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="C365" s="3" t="n">
+      <c r="C365" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="D365" t="inlineStr">
@@ -23360,13 +23357,13 @@
       <c r="T365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" t="n">
+      <c r="A366" s="1" t="n">
         <v>364</v>
       </c>
       <c r="B366" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="C366" s="3" t="n">
+      <c r="C366" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="D366" t="inlineStr">
@@ -23420,13 +23417,13 @@
       <c r="T366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" t="n">
+      <c r="A367" s="1" t="n">
         <v>365</v>
       </c>
       <c r="B367" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="C367" s="3" t="n">
+      <c r="C367" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="D367" t="inlineStr">
@@ -23480,13 +23477,13 @@
       <c r="T367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" t="n">
+      <c r="A368" s="1" t="n">
         <v>366</v>
       </c>
       <c r="B368" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="C368" s="3" t="n">
+      <c r="C368" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D368" t="inlineStr">
@@ -23540,13 +23537,13 @@
       <c r="T368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" t="n">
+      <c r="A369" s="1" t="n">
         <v>367</v>
       </c>
       <c r="B369" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="C369" s="3" t="n">
+      <c r="C369" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D369" t="inlineStr">
@@ -23600,13 +23597,13 @@
       <c r="T369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" t="n">
+      <c r="A370" s="1" t="n">
         <v>368</v>
       </c>
       <c r="B370" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="C370" s="3" t="n">
+      <c r="C370" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D370" t="inlineStr">
@@ -23660,13 +23657,13 @@
       <c r="T370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" t="n">
+      <c r="A371" s="1" t="n">
         <v>369</v>
       </c>
       <c r="B371" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="C371" s="3" t="n">
+      <c r="C371" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="D371" t="inlineStr">
@@ -23722,13 +23719,13 @@
       <c r="T371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" t="n">
+      <c r="A372" s="1" t="n">
         <v>370</v>
       </c>
       <c r="B372" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="C372" s="3" t="n">
+      <c r="C372" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="D372" t="inlineStr">
@@ -23784,13 +23781,13 @@
       <c r="T372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" t="n">
+      <c r="A373" s="1" t="n">
         <v>371</v>
       </c>
       <c r="B373" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="C373" s="3" t="n">
+      <c r="C373" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="D373" t="inlineStr">
@@ -23846,13 +23843,13 @@
       <c r="T373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" t="n">
+      <c r="A374" s="1" t="n">
         <v>372</v>
       </c>
       <c r="B374" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="C374" s="3" t="n">
+      <c r="C374" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D374" t="inlineStr">
@@ -23908,13 +23905,13 @@
       <c r="T374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" t="n">
+      <c r="A375" s="1" t="n">
         <v>373</v>
       </c>
       <c r="B375" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="C375" s="3" t="n">
+      <c r="C375" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D375" t="inlineStr">
@@ -23970,13 +23967,13 @@
       <c r="T375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" t="n">
+      <c r="A376" s="1" t="n">
         <v>374</v>
       </c>
       <c r="B376" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="C376" s="3" t="n">
+      <c r="C376" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D376" t="inlineStr">
@@ -24032,13 +24029,13 @@
       <c r="T376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" t="n">
+      <c r="A377" s="1" t="n">
         <v>375</v>
       </c>
       <c r="B377" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="C377" s="3" t="n">
+      <c r="C377" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="D377" t="inlineStr">
@@ -24092,13 +24089,13 @@
       <c r="T377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" t="n">
+      <c r="A378" s="1" t="n">
         <v>376</v>
       </c>
       <c r="B378" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="C378" s="3" t="n">
+      <c r="C378" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="D378" t="inlineStr">
@@ -24152,13 +24149,13 @@
       <c r="T378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" t="n">
+      <c r="A379" s="1" t="n">
         <v>377</v>
       </c>
       <c r="B379" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="C379" s="3" t="n">
+      <c r="C379" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="D379" t="inlineStr">
@@ -24212,13 +24209,13 @@
       <c r="T379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" t="n">
+      <c r="A380" s="1" t="n">
         <v>378</v>
       </c>
       <c r="B380" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="C380" s="3" t="n">
+      <c r="C380" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="D380" t="inlineStr">
@@ -24274,13 +24271,13 @@
       <c r="T380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" t="n">
+      <c r="A381" s="1" t="n">
         <v>379</v>
       </c>
       <c r="B381" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="C381" s="3" t="n">
+      <c r="C381" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="D381" t="inlineStr">
@@ -24336,13 +24333,13 @@
       <c r="T381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" t="n">
+      <c r="A382" s="1" t="n">
         <v>380</v>
       </c>
       <c r="B382" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="C382" s="3" t="n">
+      <c r="C382" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="D382" t="inlineStr">
@@ -24398,13 +24395,13 @@
       <c r="T382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" t="n">
+      <c r="A383" s="1" t="n">
         <v>381</v>
       </c>
       <c r="B383" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="C383" s="3" t="n">
+      <c r="C383" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D383" t="inlineStr">
@@ -24460,13 +24457,13 @@
       <c r="T383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" t="n">
+      <c r="A384" s="1" t="n">
         <v>382</v>
       </c>
       <c r="B384" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="C384" s="3" t="n">
+      <c r="C384" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D384" t="inlineStr">
@@ -24522,13 +24519,13 @@
       <c r="T384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" t="n">
+      <c r="A385" s="1" t="n">
         <v>383</v>
       </c>
       <c r="B385" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="C385" s="3" t="n">
+      <c r="C385" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D385" t="inlineStr">
@@ -24584,13 +24581,13 @@
       <c r="T385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" t="n">
+      <c r="A386" s="1" t="n">
         <v>384</v>
       </c>
       <c r="B386" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="C386" s="3" t="n">
+      <c r="C386" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="D386" t="inlineStr">
@@ -24646,13 +24643,13 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="n">
+      <c r="A387" s="1" t="n">
         <v>385</v>
       </c>
       <c r="B387" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="C387" s="3" t="n">
+      <c r="C387" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="D387" t="inlineStr">
@@ -24708,13 +24705,13 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="n">
+      <c r="A388" s="1" t="n">
         <v>386</v>
       </c>
       <c r="B388" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="C388" s="3" t="n">
+      <c r="C388" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="D388" t="inlineStr">
@@ -24770,13 +24767,13 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="n">
+      <c r="A389" s="1" t="n">
         <v>387</v>
       </c>
       <c r="B389" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="C389" s="3" t="n">
+      <c r="C389" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="D389" t="inlineStr">
@@ -24834,13 +24831,13 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="n">
+      <c r="A390" s="1" t="n">
         <v>388</v>
       </c>
       <c r="B390" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="C390" s="3" t="n">
+      <c r="C390" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="D390" t="inlineStr">
@@ -24898,13 +24895,13 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="n">
+      <c r="A391" s="1" t="n">
         <v>389</v>
       </c>
       <c r="B391" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="C391" s="3" t="n">
+      <c r="C391" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="D391" t="inlineStr">
@@ -24962,13 +24959,13 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="n">
+      <c r="A392" s="1" t="n">
         <v>390</v>
       </c>
       <c r="B392" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="C392" s="3" t="n">
+      <c r="C392" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D392" t="inlineStr">
@@ -25024,13 +25021,13 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="n">
+      <c r="A393" s="1" t="n">
         <v>391</v>
       </c>
       <c r="B393" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="C393" s="3" t="n">
+      <c r="C393" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D393" t="inlineStr">
@@ -25086,13 +25083,13 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="n">
+      <c r="A394" s="1" t="n">
         <v>392</v>
       </c>
       <c r="B394" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="C394" s="3" t="n">
+      <c r="C394" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D394" t="inlineStr">
@@ -25148,13 +25145,13 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="n">
+      <c r="A395" s="1" t="n">
         <v>393</v>
       </c>
       <c r="B395" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="C395" s="3" t="n">
+      <c r="C395" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="D395" t="inlineStr">
@@ -25206,13 +25203,13 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="n">
+      <c r="A396" s="1" t="n">
         <v>394</v>
       </c>
       <c r="B396" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="C396" s="3" t="n">
+      <c r="C396" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="D396" t="inlineStr">
@@ -25264,13 +25261,13 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="n">
+      <c r="A397" s="1" t="n">
         <v>395</v>
       </c>
       <c r="B397" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="C397" s="3" t="n">
+      <c r="C397" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="D397" t="inlineStr">
@@ -25322,13 +25319,13 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="n">
+      <c r="A398" s="1" t="n">
         <v>396</v>
       </c>
       <c r="B398" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="C398" s="3" t="n">
+      <c r="C398" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="D398" t="inlineStr">
@@ -25386,13 +25383,13 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="n">
+      <c r="A399" s="1" t="n">
         <v>397</v>
       </c>
       <c r="B399" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="C399" s="3" t="n">
+      <c r="C399" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="D399" t="inlineStr">
@@ -25450,13 +25447,13 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="n">
+      <c r="A400" s="1" t="n">
         <v>398</v>
       </c>
       <c r="B400" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="C400" s="3" t="n">
+      <c r="C400" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="D400" t="inlineStr">
@@ -25514,13 +25511,13 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="n">
+      <c r="A401" s="1" t="n">
         <v>399</v>
       </c>
       <c r="B401" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="C401" s="3" t="n">
+      <c r="C401" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="D401" t="inlineStr">
@@ -25578,13 +25575,13 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="n">
+      <c r="A402" s="1" t="n">
         <v>400</v>
       </c>
       <c r="B402" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="C402" s="3" t="n">
+      <c r="C402" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="D402" t="inlineStr">
@@ -25642,13 +25639,13 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
+      <c r="A403" s="1" t="n">
         <v>401</v>
       </c>
       <c r="B403" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="C403" s="3" t="n">
+      <c r="C403" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="D403" t="inlineStr">
@@ -25706,13 +25703,13 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="n">
+      <c r="A404" s="1" t="n">
         <v>402</v>
       </c>
       <c r="B404" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="C404" s="3" t="n">
+      <c r="C404" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="D404" t="inlineStr">
@@ -25770,13 +25767,13 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="n">
+      <c r="A405" s="1" t="n">
         <v>403</v>
       </c>
       <c r="B405" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="C405" s="3" t="n">
+      <c r="C405" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="D405" t="inlineStr">
@@ -25834,13 +25831,13 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="n">
+      <c r="A406" s="1" t="n">
         <v>404</v>
       </c>
       <c r="B406" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="C406" s="3" t="n">
+      <c r="C406" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="D406" t="inlineStr">
@@ -25898,13 +25895,13 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="n">
+      <c r="A407" s="1" t="n">
         <v>405</v>
       </c>
       <c r="B407" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="C407" s="3" t="n">
+      <c r="C407" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="D407" t="inlineStr">
@@ -25946,13 +25943,13 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="n">
+      <c r="A408" s="1" t="n">
         <v>406</v>
       </c>
       <c r="B408" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="C408" s="3" t="n">
+      <c r="C408" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="D408" t="inlineStr">
@@ -25994,13 +25991,13 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="n">
+      <c r="A409" s="1" t="n">
         <v>407</v>
       </c>
       <c r="B409" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="C409" s="3" t="n">
+      <c r="C409" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="D409" t="inlineStr">
@@ -26042,13 +26039,13 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="n">
+      <c r="A410" s="1" t="n">
         <v>408</v>
       </c>
       <c r="B410" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="C410" s="3" t="n">
+      <c r="C410" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D410" t="inlineStr">
@@ -26090,13 +26087,13 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="n">
+      <c r="A411" s="1" t="n">
         <v>409</v>
       </c>
       <c r="B411" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="C411" s="3" t="n">
+      <c r="C411" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D411" t="inlineStr">
@@ -26138,13 +26135,13 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="n">
+      <c r="A412" s="1" t="n">
         <v>410</v>
       </c>
       <c r="B412" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="C412" s="3" t="n">
+      <c r="C412" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D412" t="inlineStr">
@@ -26186,13 +26183,13 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="n">
+      <c r="A413" s="1" t="n">
         <v>411</v>
       </c>
       <c r="B413" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="C413" s="3" t="n">
+      <c r="C413" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="D413" t="inlineStr">
@@ -26236,13 +26233,13 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="n">
+      <c r="A414" s="1" t="n">
         <v>412</v>
       </c>
       <c r="B414" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="C414" s="3" t="n">
+      <c r="C414" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="D414" t="inlineStr">
@@ -26286,13 +26283,13 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="n">
+      <c r="A415" s="1" t="n">
         <v>413</v>
       </c>
       <c r="B415" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="C415" s="3" t="n">
+      <c r="C415" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="D415" t="inlineStr">
@@ -26336,13 +26333,13 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="n">
+      <c r="A416" s="1" t="n">
         <v>414</v>
       </c>
       <c r="B416" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="C416" s="3" t="n">
+      <c r="C416" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="D416" t="inlineStr">
@@ -26386,13 +26383,13 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="n">
+      <c r="A417" s="1" t="n">
         <v>415</v>
       </c>
       <c r="B417" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="C417" s="3" t="n">
+      <c r="C417" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="D417" t="inlineStr">
@@ -26436,13 +26433,13 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="n">
+      <c r="A418" s="1" t="n">
         <v>416</v>
       </c>
       <c r="B418" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="C418" s="3" t="n">
+      <c r="C418" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="D418" t="inlineStr">
@@ -26486,13 +26483,13 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="n">
+      <c r="A419" s="1" t="n">
         <v>417</v>
       </c>
       <c r="B419" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C419" s="3" t="n">
+      <c r="C419" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="D419" t="inlineStr">
@@ -26550,13 +26547,13 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="n">
+      <c r="A420" s="1" t="n">
         <v>418</v>
       </c>
       <c r="B420" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C420" s="3" t="n">
+      <c r="C420" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="D420" t="inlineStr">
@@ -26614,13 +26611,13 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="n">
+      <c r="A421" s="1" t="n">
         <v>419</v>
       </c>
       <c r="B421" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="C421" s="3" t="n">
+      <c r="C421" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="D421" t="inlineStr">
@@ -26678,13 +26675,13 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
+      <c r="A422" s="1" t="n">
         <v>420</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="C422" s="3" t="n">
+      <c r="C422" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="D422" t="inlineStr">
@@ -26742,13 +26739,13 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="n">
+      <c r="A423" s="1" t="n">
         <v>421</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="C423" s="3" t="n">
+      <c r="C423" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="D423" t="inlineStr">
@@ -26806,13 +26803,13 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="n">
+      <c r="A424" s="1" t="n">
         <v>422</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="C424" s="3" t="n">
+      <c r="C424" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="D424" t="inlineStr">
@@ -26868,13 +26865,13 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="1" t="n">
         <v>423</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="C425" s="3" t="n">
+      <c r="C425" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="D425" t="inlineStr">
@@ -26930,13 +26927,13 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="n">
+      <c r="A426" s="1" t="n">
         <v>424</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="C426" s="3" t="n">
+      <c r="C426" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="D426" t="inlineStr">
@@ -26992,13 +26989,13 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="n">
+      <c r="A427" s="1" t="n">
         <v>425</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="C427" s="3" t="n">
+      <c r="C427" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="D427" t="inlineStr">
@@ -27054,13 +27051,13 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="n">
+      <c r="A428" s="1" t="n">
         <v>426</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C428" s="3" t="n">
+      <c r="C428" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="D428" t="inlineStr">
@@ -27118,13 +27115,13 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="n">
+      <c r="A429" s="1" t="n">
         <v>427</v>
       </c>
       <c r="B429" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C429" s="3" t="n">
+      <c r="C429" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="D429" t="inlineStr">
@@ -27182,13 +27179,13 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="n">
+      <c r="A430" s="1" t="n">
         <v>428</v>
       </c>
       <c r="B430" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C430" s="3" t="n">
+      <c r="C430" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="D430" t="inlineStr">
@@ -27246,13 +27243,13 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="n">
+      <c r="A431" s="1" t="n">
         <v>429</v>
       </c>
       <c r="B431" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="C431" s="3" t="n">
+      <c r="C431" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="D431" t="inlineStr">
@@ -27310,13 +27307,13 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="n">
+      <c r="A432" s="1" t="n">
         <v>430</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="C432" s="3" t="n">
+      <c r="C432" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="D432" t="inlineStr">
@@ -27374,13 +27371,13 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="n">
+      <c r="A433" s="1" t="n">
         <v>431</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="C433" s="3" t="n">
+      <c r="C433" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="D433" t="inlineStr">
@@ -27438,13 +27435,13 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="n">
+      <c r="A434" s="1" t="n">
         <v>432</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="C434" s="3" t="n">
+      <c r="C434" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="D434" t="inlineStr">
@@ -27490,13 +27487,13 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="n">
+      <c r="A435" s="1" t="n">
         <v>433</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="C435" s="3" t="n">
+      <c r="C435" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="D435" t="inlineStr">
@@ -27542,13 +27539,13 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
+      <c r="A436" s="1" t="n">
         <v>434</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="C436" s="3" t="n">
+      <c r="C436" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="D436" t="inlineStr">
@@ -27594,13 +27591,13 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
+      <c r="A437" s="1" t="n">
         <v>435</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="C437" s="3" t="n">
+      <c r="C437" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="D437" t="inlineStr">
@@ -27658,13 +27655,13 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
+      <c r="A438" s="1" t="n">
         <v>436</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="C438" s="3" t="n">
+      <c r="C438" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="D438" t="inlineStr">
@@ -27722,13 +27719,13 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="1" t="n">
         <v>437</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="C439" s="3" t="n">
+      <c r="C439" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="D439" t="inlineStr">
@@ -27786,13 +27783,13 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="1" t="n">
         <v>438</v>
       </c>
       <c r="B440" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="C440" s="3" t="n">
+      <c r="C440" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D440" t="inlineStr">
@@ -27846,13 +27843,13 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="1" t="n">
         <v>439</v>
       </c>
       <c r="B441" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="C441" s="3" t="n">
+      <c r="C441" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D441" t="inlineStr">
@@ -27906,13 +27903,13 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="n">
+      <c r="A442" s="1" t="n">
         <v>440</v>
       </c>
       <c r="B442" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="C442" s="3" t="n">
+      <c r="C442" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D442" t="inlineStr">
@@ -27966,13 +27963,13 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="1" t="n">
         <v>441</v>
       </c>
       <c r="B443" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="C443" s="3" t="n">
+      <c r="C443" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D443" t="inlineStr">
@@ -28030,13 +28027,13 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="1" t="n">
         <v>442</v>
       </c>
       <c r="B444" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="C444" s="3" t="n">
+      <c r="C444" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D444" t="inlineStr">
@@ -28094,13 +28091,13 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="n">
+      <c r="A445" s="1" t="n">
         <v>443</v>
       </c>
       <c r="B445" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="C445" s="3" t="n">
+      <c r="C445" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="D445" t="inlineStr">
@@ -28158,13 +28155,13 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
+      <c r="A446" s="1" t="n">
         <v>444</v>
       </c>
       <c r="B446" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C446" s="3" t="n">
+      <c r="C446" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="D446" t="inlineStr">
@@ -28222,13 +28219,13 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
+      <c r="A447" s="1" t="n">
         <v>445</v>
       </c>
       <c r="B447" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C447" s="3" t="n">
+      <c r="C447" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="D447" t="inlineStr">
@@ -28286,13 +28283,13 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
+      <c r="A448" s="1" t="n">
         <v>446</v>
       </c>
       <c r="B448" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="C448" s="3" t="n">
+      <c r="C448" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="D448" t="inlineStr">
@@ -28350,13 +28347,13 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
+      <c r="A449" s="1" t="n">
         <v>447</v>
       </c>
       <c r="B449" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="C449" s="3" t="n">
+      <c r="C449" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="D449" t="inlineStr">
@@ -28414,13 +28411,13 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
+      <c r="A450" s="1" t="n">
         <v>448</v>
       </c>
       <c r="B450" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="C450" s="3" t="n">
+      <c r="C450" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="D450" t="inlineStr">
@@ -28478,13 +28475,13 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="1" t="n">
         <v>449</v>
       </c>
       <c r="B451" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="C451" s="3" t="n">
+      <c r="C451" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="D451" t="inlineStr">
@@ -28542,13 +28539,13 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
+      <c r="A452" s="1" t="n">
         <v>450</v>
       </c>
       <c r="B452" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="C452" s="3" t="n">
+      <c r="C452" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="D452" t="inlineStr">
@@ -28606,13 +28603,13 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
+      <c r="A453" s="1" t="n">
         <v>451</v>
       </c>
       <c r="B453" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="C453" s="3" t="n">
+      <c r="C453" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="D453" t="inlineStr">
@@ -28670,13 +28667,13 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
+      <c r="A454" s="1" t="n">
         <v>452</v>
       </c>
       <c r="B454" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="C454" s="3" t="n">
+      <c r="C454" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="D454" t="inlineStr">
@@ -28734,13 +28731,13 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
+      <c r="A455" s="1" t="n">
         <v>453</v>
       </c>
       <c r="B455" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C455" s="3" t="n">
+      <c r="C455" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="D455" t="inlineStr">
@@ -28798,13 +28795,13 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
+      <c r="A456" s="1" t="n">
         <v>454</v>
       </c>
       <c r="B456" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C456" s="3" t="n">
+      <c r="C456" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="D456" t="inlineStr">
@@ -28862,13 +28859,13 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
+      <c r="A457" s="1" t="n">
         <v>455</v>
       </c>
       <c r="B457" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C457" s="3" t="n">
+      <c r="C457" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="D457" t="inlineStr">
@@ -28926,13 +28923,13 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
+      <c r="A458" s="1" t="n">
         <v>456</v>
       </c>
       <c r="B458" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="C458" s="3" t="n">
+      <c r="C458" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="D458" t="inlineStr">
@@ -28990,13 +28987,13 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
+      <c r="A459" s="1" t="n">
         <v>457</v>
       </c>
       <c r="B459" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="C459" s="3" t="n">
+      <c r="C459" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="D459" t="inlineStr">
@@ -29054,13 +29051,13 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
+      <c r="A460" s="1" t="n">
         <v>458</v>
       </c>
       <c r="B460" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="C460" s="3" t="n">
+      <c r="C460" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="D460" t="inlineStr">
@@ -29118,13 +29115,13 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
+      <c r="A461" s="1" t="n">
         <v>459</v>
       </c>
       <c r="B461" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C461" s="3" t="n">
+      <c r="C461" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="D461" t="inlineStr">
@@ -29182,13 +29179,13 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
+      <c r="A462" s="1" t="n">
         <v>460</v>
       </c>
       <c r="B462" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C462" s="3" t="n">
+      <c r="C462" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="D462" t="inlineStr">
@@ -29246,13 +29243,13 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
+      <c r="A463" s="1" t="n">
         <v>461</v>
       </c>
       <c r="B463" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C463" s="3" t="n">
+      <c r="C463" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="D463" t="inlineStr">
@@ -29310,13 +29307,13 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
+      <c r="A464" s="1" t="n">
         <v>462</v>
       </c>
       <c r="B464" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="C464" s="3" t="n">
+      <c r="C464" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="D464" t="inlineStr">
@@ -29374,13 +29371,13 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
+      <c r="A465" s="1" t="n">
         <v>463</v>
       </c>
       <c r="B465" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="C465" s="3" t="n">
+      <c r="C465" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="D465" t="inlineStr">
@@ -29438,13 +29435,13 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
+      <c r="A466" s="1" t="n">
         <v>464</v>
       </c>
       <c r="B466" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="C466" s="3" t="n">
+      <c r="C466" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="D466" t="inlineStr">
@@ -29502,13 +29499,13 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
+      <c r="A467" s="1" t="n">
         <v>465</v>
       </c>
       <c r="B467" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="C467" s="3" t="n">
+      <c r="C467" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="D467" t="inlineStr">
@@ -29566,13 +29563,13 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
+      <c r="A468" s="1" t="n">
         <v>466</v>
       </c>
       <c r="B468" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="C468" s="3" t="n">
+      <c r="C468" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="D468" t="inlineStr">
@@ -29630,13 +29627,13 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
+      <c r="A469" s="1" t="n">
         <v>467</v>
       </c>
       <c r="B469" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="C469" s="3" t="n">
+      <c r="C469" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="D469" t="inlineStr">
@@ -29694,13 +29691,13 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
+      <c r="A470" s="1" t="n">
         <v>468</v>
       </c>
       <c r="B470" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="C470" s="3" t="n">
+      <c r="C470" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="D470" t="inlineStr">
@@ -29758,13 +29755,13 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
+      <c r="A471" s="1" t="n">
         <v>469</v>
       </c>
       <c r="B471" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="C471" s="3" t="n">
+      <c r="C471" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="D471" t="inlineStr">
@@ -29822,13 +29819,13 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
+      <c r="A472" s="1" t="n">
         <v>470</v>
       </c>
       <c r="B472" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="C472" s="3" t="n">
+      <c r="C472" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="D472" t="inlineStr">
@@ -29886,13 +29883,13 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
+      <c r="A473" s="1" t="n">
         <v>471</v>
       </c>
       <c r="B473" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="C473" s="3" t="n">
+      <c r="C473" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="D473" t="inlineStr">
@@ -29950,13 +29947,13 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
+      <c r="A474" s="1" t="n">
         <v>472</v>
       </c>
       <c r="B474" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="C474" s="3" t="n">
+      <c r="C474" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="D474" t="inlineStr">
@@ -30014,13 +30011,13 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
+      <c r="A475" s="1" t="n">
         <v>473</v>
       </c>
       <c r="B475" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="C475" s="3" t="n">
+      <c r="C475" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="D475" t="inlineStr">
@@ -30078,13 +30075,13 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
+      <c r="A476" s="1" t="n">
         <v>474</v>
       </c>
       <c r="B476" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="C476" s="3" t="n">
+      <c r="C476" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="D476" t="inlineStr">
@@ -30138,13 +30135,13 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
+      <c r="A477" s="1" t="n">
         <v>475</v>
       </c>
       <c r="B477" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="C477" s="3" t="n">
+      <c r="C477" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="D477" t="inlineStr">
@@ -30198,13 +30195,13 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
+      <c r="A478" s="1" t="n">
         <v>476</v>
       </c>
       <c r="B478" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="C478" s="3" t="n">
+      <c r="C478" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="D478" t="inlineStr">
@@ -30258,13 +30255,13 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
+      <c r="A479" s="1" t="n">
         <v>477</v>
       </c>
       <c r="B479" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C479" s="3" t="n">
+      <c r="C479" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="D479" t="inlineStr">
@@ -30322,13 +30319,13 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
+      <c r="A480" s="1" t="n">
         <v>478</v>
       </c>
       <c r="B480" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C480" s="3" t="n">
+      <c r="C480" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="D480" t="inlineStr">
@@ -30386,13 +30383,13 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
+      <c r="A481" s="1" t="n">
         <v>479</v>
       </c>
       <c r="B481" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C481" s="3" t="n">
+      <c r="C481" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="D481" t="inlineStr">
@@ -30450,13 +30447,13 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
+      <c r="A482" s="1" t="n">
         <v>480</v>
       </c>
       <c r="B482" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C482" s="3" t="n">
+      <c r="C482" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="D482" t="inlineStr">
@@ -30514,13 +30511,13 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
+      <c r="A483" s="1" t="n">
         <v>481</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C483" s="3" t="n">
+      <c r="C483" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="D483" t="inlineStr">
@@ -30578,13 +30575,13 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
+      <c r="A484" s="1" t="n">
         <v>482</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C484" s="3" t="n">
+      <c r="C484" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="D484" t="inlineStr">
@@ -30642,13 +30639,13 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
+      <c r="A485" s="1" t="n">
         <v>483</v>
       </c>
       <c r="B485" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="C485" s="3" t="n">
+      <c r="C485" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="D485" t="inlineStr">
@@ -30706,13 +30703,13 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
+      <c r="A486" s="1" t="n">
         <v>484</v>
       </c>
       <c r="B486" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="C486" s="3" t="n">
+      <c r="C486" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="D486" t="inlineStr">
@@ -30770,13 +30767,13 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
+      <c r="A487" s="1" t="n">
         <v>485</v>
       </c>
       <c r="B487" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="C487" s="3" t="n">
+      <c r="C487" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="D487" t="inlineStr">
@@ -30834,13 +30831,13 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
+      <c r="A488" s="1" t="n">
         <v>486</v>
       </c>
       <c r="B488" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C488" s="3" t="n">
+      <c r="C488" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="D488" t="inlineStr">
@@ -30898,13 +30895,13 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
+      <c r="A489" s="1" t="n">
         <v>487</v>
       </c>
       <c r="B489" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C489" s="3" t="n">
+      <c r="C489" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="D489" t="inlineStr">
@@ -30962,13 +30959,13 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
+      <c r="A490" s="1" t="n">
         <v>488</v>
       </c>
       <c r="B490" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C490" s="3" t="n">
+      <c r="C490" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="D490" t="inlineStr">
@@ -31026,13 +31023,13 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
+      <c r="A491" s="1" t="n">
         <v>489</v>
       </c>
       <c r="B491" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="C491" s="3" t="n">
+      <c r="C491" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="D491" t="inlineStr">
@@ -31090,13 +31087,13 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
+      <c r="A492" s="1" t="n">
         <v>490</v>
       </c>
       <c r="B492" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="C492" s="3" t="n">
+      <c r="C492" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="D492" t="inlineStr">
@@ -31154,13 +31151,13 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
+      <c r="A493" s="1" t="n">
         <v>491</v>
       </c>
       <c r="B493" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="C493" s="3" t="n">
+      <c r="C493" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="D493" t="inlineStr">
@@ -31218,13 +31215,13 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="n">
+      <c r="A494" s="1" t="n">
         <v>492</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="C494" s="3" t="n">
+      <c r="C494" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D494" t="inlineStr">
@@ -31280,13 +31277,13 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
+      <c r="A495" s="1" t="n">
         <v>493</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="C495" s="3" t="n">
+      <c r="C495" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D495" t="inlineStr">
@@ -31342,13 +31339,13 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="n">
+      <c r="A496" s="1" t="n">
         <v>494</v>
       </c>
       <c r="B496" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="C496" s="3" t="n">
+      <c r="C496" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D496" t="inlineStr">
@@ -31404,13 +31401,13 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
+      <c r="A497" s="1" t="n">
         <v>495</v>
       </c>
       <c r="B497" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="C497" s="3" t="n">
+      <c r="C497" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="D497" t="inlineStr">
@@ -31468,13 +31465,13 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
+      <c r="A498" s="1" t="n">
         <v>496</v>
       </c>
       <c r="B498" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="C498" s="3" t="n">
+      <c r="C498" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="D498" t="inlineStr">
@@ -31532,13 +31529,13 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
+      <c r="A499" s="1" t="n">
         <v>497</v>
       </c>
       <c r="B499" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="C499" s="3" t="n">
+      <c r="C499" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="D499" t="inlineStr">
@@ -31596,13 +31593,13 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
+      <c r="A500" s="1" t="n">
         <v>498</v>
       </c>
       <c r="B500" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="C500" s="3" t="n">
+      <c r="C500" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D500" t="inlineStr">
@@ -31660,13 +31657,13 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
+      <c r="A501" s="1" t="n">
         <v>499</v>
       </c>
       <c r="B501" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="C501" s="3" t="n">
+      <c r="C501" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D501" t="inlineStr">
@@ -31724,13 +31721,13 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
+      <c r="A502" s="1" t="n">
         <v>500</v>
       </c>
       <c r="B502" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="C502" s="3" t="n">
+      <c r="C502" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D502" t="inlineStr">
@@ -31788,13 +31785,13 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
+      <c r="A503" s="1" t="n">
         <v>501</v>
       </c>
       <c r="B503" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="C503" s="3" t="n">
+      <c r="C503" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D503" t="inlineStr">
@@ -31852,13 +31849,13 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
+      <c r="A504" s="1" t="n">
         <v>502</v>
       </c>
       <c r="B504" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="C504" s="3" t="n">
+      <c r="C504" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D504" t="inlineStr">
@@ -31916,13 +31913,13 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
+      <c r="A505" s="1" t="n">
         <v>503</v>
       </c>
       <c r="B505" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="C505" s="3" t="n">
+      <c r="C505" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="D505" t="inlineStr">
@@ -31980,13 +31977,13 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
+      <c r="A506" s="1" t="n">
         <v>504</v>
       </c>
       <c r="B506" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="C506" s="3" t="n">
+      <c r="C506" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="D506" t="inlineStr">
@@ -32040,13 +32037,13 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
+      <c r="A507" s="1" t="n">
         <v>505</v>
       </c>
       <c r="B507" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="C507" s="3" t="n">
+      <c r="C507" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="D507" t="inlineStr">
@@ -32100,13 +32097,13 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
+      <c r="A508" s="1" t="n">
         <v>506</v>
       </c>
       <c r="B508" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="C508" s="3" t="n">
+      <c r="C508" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="D508" t="inlineStr">
@@ -32160,13 +32157,13 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
+      <c r="A509" s="1" t="n">
         <v>507</v>
       </c>
       <c r="B509" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="C509" s="3" t="n">
+      <c r="C509" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="D509" t="inlineStr">
@@ -32224,13 +32221,13 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
+      <c r="A510" s="1" t="n">
         <v>508</v>
       </c>
       <c r="B510" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="C510" s="3" t="n">
+      <c r="C510" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="D510" t="inlineStr">
@@ -32288,13 +32285,13 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="n">
+      <c r="A511" s="1" t="n">
         <v>509</v>
       </c>
       <c r="B511" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="C511" s="3" t="n">
+      <c r="C511" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="D511" t="inlineStr">
@@ -32352,13 +32349,13 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
+      <c r="A512" s="1" t="n">
         <v>510</v>
       </c>
       <c r="B512" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="C512" s="3" t="n">
+      <c r="C512" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D512" t="inlineStr">
@@ -32412,13 +32409,13 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="n">
+      <c r="A513" s="1" t="n">
         <v>511</v>
       </c>
       <c r="B513" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="C513" s="3" t="n">
+      <c r="C513" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D513" t="inlineStr">
@@ -32472,13 +32469,13 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
+      <c r="A514" s="1" t="n">
         <v>512</v>
       </c>
       <c r="B514" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="C514" s="3" t="n">
+      <c r="C514" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D514" t="inlineStr">
@@ -32532,13 +32529,13 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="n">
+      <c r="A515" s="1" t="n">
         <v>513</v>
       </c>
       <c r="B515" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C515" s="3" t="n">
+      <c r="C515" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D515" t="inlineStr">
@@ -32596,13 +32593,13 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="n">
+      <c r="A516" s="1" t="n">
         <v>514</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C516" s="3" t="n">
+      <c r="C516" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D516" t="inlineStr">
@@ -32660,13 +32657,13 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
+      <c r="A517" s="1" t="n">
         <v>515</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="C517" s="3" t="n">
+      <c r="C517" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="D517" t="inlineStr">
@@ -32724,13 +32721,13 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="n">
+      <c r="A518" s="1" t="n">
         <v>516</v>
       </c>
       <c r="B518" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="C518" s="3" t="n">
+      <c r="C518" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D518" t="inlineStr">
@@ -32788,13 +32785,13 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="n">
+      <c r="A519" s="1" t="n">
         <v>517</v>
       </c>
       <c r="B519" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="C519" s="3" t="n">
+      <c r="C519" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D519" t="inlineStr">
@@ -32852,13 +32849,13 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="n">
+      <c r="A520" s="1" t="n">
         <v>518</v>
       </c>
       <c r="B520" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="C520" s="3" t="n">
+      <c r="C520" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D520" t="inlineStr">
@@ -32916,13 +32913,13 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="n">
+      <c r="A521" s="1" t="n">
         <v>519</v>
       </c>
       <c r="B521" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="C521" s="3" t="n">
+      <c r="C521" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D521" t="inlineStr">
@@ -32980,13 +32977,13 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="n">
+      <c r="A522" s="1" t="n">
         <v>520</v>
       </c>
       <c r="B522" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="C522" s="3" t="n">
+      <c r="C522" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D522" t="inlineStr">
@@ -33044,13 +33041,13 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
+      <c r="A523" s="1" t="n">
         <v>521</v>
       </c>
       <c r="B523" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="C523" s="3" t="n">
+      <c r="C523" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D523" t="inlineStr">
@@ -33108,13 +33105,13 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="n">
+      <c r="A524" s="1" t="n">
         <v>522</v>
       </c>
       <c r="B524" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C524" s="3" t="n">
+      <c r="C524" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="D524" t="inlineStr">
@@ -33172,13 +33169,13 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="n">
+      <c r="A525" s="1" t="n">
         <v>523</v>
       </c>
       <c r="B525" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C525" s="3" t="n">
+      <c r="C525" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="D525" t="inlineStr">
@@ -33236,13 +33233,13 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="n">
+      <c r="A526" s="1" t="n">
         <v>524</v>
       </c>
       <c r="B526" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="C526" s="3" t="n">
+      <c r="C526" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="D526" t="inlineStr">
@@ -33300,13 +33297,13 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="n">
+      <c r="A527" s="1" t="n">
         <v>525</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="C527" s="3" t="n">
+      <c r="C527" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D527" t="inlineStr">
@@ -33364,13 +33361,13 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="n">
+      <c r="A528" s="1" t="n">
         <v>526</v>
       </c>
       <c r="B528" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="C528" s="3" t="n">
+      <c r="C528" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D528" t="inlineStr">
@@ -33428,13 +33425,13 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="n">
+      <c r="A529" s="1" t="n">
         <v>527</v>
       </c>
       <c r="B529" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="C529" s="3" t="n">
+      <c r="C529" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D529" t="inlineStr">
@@ -33492,13 +33489,13 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="n">
+      <c r="A530" s="1" t="n">
         <v>528</v>
       </c>
       <c r="B530" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="C530" s="3" t="n">
+      <c r="C530" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D530" t="inlineStr">
@@ -33556,13 +33553,13 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="n">
+      <c r="A531" s="1" t="n">
         <v>529</v>
       </c>
       <c r="B531" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="C531" s="3" t="n">
+      <c r="C531" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D531" t="inlineStr">
@@ -33620,13 +33617,13 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="n">
+      <c r="A532" s="1" t="n">
         <v>530</v>
       </c>
       <c r="B532" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="C532" s="3" t="n">
+      <c r="C532" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D532" t="inlineStr">
@@ -33684,13 +33681,13 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="n">
+      <c r="A533" s="1" t="n">
         <v>531</v>
       </c>
       <c r="B533" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C533" s="3" t="n">
+      <c r="C533" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="D533" t="inlineStr">
@@ -33748,13 +33745,13 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="n">
+      <c r="A534" s="1" t="n">
         <v>532</v>
       </c>
       <c r="B534" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C534" s="3" t="n">
+      <c r="C534" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="D534" t="inlineStr">
@@ -33812,13 +33809,13 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="n">
+      <c r="A535" s="1" t="n">
         <v>533</v>
       </c>
       <c r="B535" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="C535" s="3" t="n">
+      <c r="C535" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="D535" t="inlineStr">
@@ -33876,13 +33873,13 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="n">
+      <c r="A536" s="1" t="n">
         <v>534</v>
       </c>
       <c r="B536" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="C536" s="3" t="n">
+      <c r="C536" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D536" t="inlineStr">
@@ -33938,13 +33935,13 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="n">
+      <c r="A537" s="1" t="n">
         <v>535</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="C537" s="3" t="n">
+      <c r="C537" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D537" t="inlineStr">
@@ -34000,13 +33997,13 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="n">
+      <c r="A538" s="1" t="n">
         <v>536</v>
       </c>
       <c r="B538" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="C538" s="3" t="n">
+      <c r="C538" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D538" t="inlineStr">
@@ -34062,13 +34059,13 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="n">
+      <c r="A539" s="1" t="n">
         <v>537</v>
       </c>
       <c r="B539" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="C539" s="3" t="n">
+      <c r="C539" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
@@ -34124,13 +34121,13 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="n">
+      <c r="A540" s="1" t="n">
         <v>538</v>
       </c>
       <c r="B540" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="C540" s="3" t="n">
+      <c r="C540" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
@@ -34186,13 +34183,13 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="n">
+      <c r="A541" s="1" t="n">
         <v>539</v>
       </c>
       <c r="B541" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="C541" s="3" t="n">
+      <c r="C541" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
@@ -34248,13 +34245,13 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="n">
+      <c r="A542" s="1" t="n">
         <v>540</v>
       </c>
       <c r="B542" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="C542" s="3" t="n">
+      <c r="C542" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="D542" t="inlineStr">
@@ -34310,13 +34307,13 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="n">
+      <c r="A543" s="1" t="n">
         <v>541</v>
       </c>
       <c r="B543" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="C543" s="3" t="n">
+      <c r="C543" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="D543" t="inlineStr">
@@ -34372,13 +34369,13 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="n">
+      <c r="A544" s="1" t="n">
         <v>542</v>
       </c>
       <c r="B544" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="C544" s="3" t="n">
+      <c r="C544" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="D544" t="inlineStr">
@@ -34434,13 +34431,13 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="n">
+      <c r="A545" s="1" t="n">
         <v>543</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="C545" s="3" t="n">
+      <c r="C545" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D545" t="inlineStr">
@@ -34498,13 +34495,13 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="n">
+      <c r="A546" s="1" t="n">
         <v>544</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="C546" s="3" t="n">
+      <c r="C546" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D546" t="inlineStr">
@@ -34562,13 +34559,13 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="n">
+      <c r="A547" s="1" t="n">
         <v>545</v>
       </c>
       <c r="B547" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="C547" s="3" t="n">
+      <c r="C547" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D547" t="inlineStr">
@@ -34626,13 +34623,13 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="n">
+      <c r="A548" s="1" t="n">
         <v>546</v>
       </c>
       <c r="B548" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="C548" s="3" t="n">
+      <c r="C548" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
@@ -34690,13 +34687,13 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="n">
+      <c r="A549" s="1" t="n">
         <v>547</v>
       </c>
       <c r="B549" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="C549" s="3" t="n">
+      <c r="C549" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
@@ -34754,13 +34751,13 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="n">
+      <c r="A550" s="1" t="n">
         <v>548</v>
       </c>
       <c r="B550" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="C550" s="3" t="n">
+      <c r="C550" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
@@ -34818,13 +34815,13 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="n">
+      <c r="A551" s="1" t="n">
         <v>549</v>
       </c>
       <c r="B551" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="C551" s="3" t="n">
+      <c r="C551" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="D551" t="inlineStr">
@@ -34874,13 +34871,13 @@
       <c r="T551" t="inlineStr"/>
     </row>
     <row r="552">
-      <c r="A552" t="n">
+      <c r="A552" s="1" t="n">
         <v>550</v>
       </c>
       <c r="B552" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="C552" s="3" t="n">
+      <c r="C552" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="D552" t="inlineStr">
@@ -34930,13 +34927,13 @@
       <c r="T552" t="inlineStr"/>
     </row>
     <row r="553">
-      <c r="A553" t="n">
+      <c r="A553" s="1" t="n">
         <v>551</v>
       </c>
       <c r="B553" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="C553" s="3" t="n">
+      <c r="C553" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="D553" t="inlineStr">
@@ -34986,13 +34983,13 @@
       <c r="T553" t="inlineStr"/>
     </row>
     <row r="554">
-      <c r="A554" t="n">
+      <c r="A554" s="1" t="n">
         <v>552</v>
       </c>
       <c r="B554" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="C554" s="3" t="n">
+      <c r="C554" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D554" t="inlineStr">
@@ -35050,13 +35047,13 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="n">
+      <c r="A555" s="1" t="n">
         <v>553</v>
       </c>
       <c r="B555" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="C555" s="3" t="n">
+      <c r="C555" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D555" t="inlineStr">
@@ -35114,13 +35111,13 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="n">
+      <c r="A556" s="1" t="n">
         <v>554</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="C556" s="3" t="n">
+      <c r="C556" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D556" t="inlineStr">
@@ -35178,13 +35175,13 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="n">
+      <c r="A557" s="1" t="n">
         <v>555</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="C557" s="3" t="n">
+      <c r="C557" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D557" t="inlineStr">
@@ -35242,13 +35239,13 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="n">
+      <c r="A558" s="1" t="n">
         <v>556</v>
       </c>
       <c r="B558" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="C558" s="3" t="n">
+      <c r="C558" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D558" t="inlineStr">
@@ -35306,13 +35303,13 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="n">
+      <c r="A559" s="1" t="n">
         <v>557</v>
       </c>
       <c r="B559" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="C559" s="3" t="n">
+      <c r="C559" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="D559" t="inlineStr">
@@ -35370,13 +35367,13 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="n">
+      <c r="A560" s="1" t="n">
         <v>558</v>
       </c>
       <c r="B560" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="C560" s="3" t="n">
+      <c r="C560" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="D560" t="inlineStr">
@@ -35434,13 +35431,13 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="n">
+      <c r="A561" s="1" t="n">
         <v>559</v>
       </c>
       <c r="B561" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="C561" s="3" t="n">
+      <c r="C561" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="D561" t="inlineStr">
@@ -35498,13 +35495,13 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="n">
+      <c r="A562" s="1" t="n">
         <v>560</v>
       </c>
       <c r="B562" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="C562" s="3" t="n">
+      <c r="C562" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="D562" t="inlineStr">
@@ -35562,13 +35559,13 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="n">
+      <c r="A563" s="1" t="n">
         <v>561</v>
       </c>
       <c r="B563" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="C563" s="3" t="n">
+      <c r="C563" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D563" t="inlineStr">
@@ -35626,13 +35623,13 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="n">
+      <c r="A564" s="1" t="n">
         <v>562</v>
       </c>
       <c r="B564" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="C564" s="3" t="n">
+      <c r="C564" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D564" t="inlineStr">
@@ -35690,13 +35687,13 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="n">
+      <c r="A565" s="1" t="n">
         <v>563</v>
       </c>
       <c r="B565" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="C565" s="3" t="n">
+      <c r="C565" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D565" t="inlineStr">
@@ -35754,13 +35751,13 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="n">
+      <c r="A566" s="1" t="n">
         <v>564</v>
       </c>
       <c r="B566" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="C566" s="3" t="n">
+      <c r="C566" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="D566" t="inlineStr">
@@ -35812,13 +35809,13 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="n">
+      <c r="A567" s="1" t="n">
         <v>565</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="C567" s="3" t="n">
+      <c r="C567" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="D567" t="inlineStr">
@@ -35870,13 +35867,13 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="n">
+      <c r="A568" s="1" t="n">
         <v>566</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="C568" s="3" t="n">
+      <c r="C568" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="D568" t="inlineStr">
@@ -35928,13 +35925,13 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="n">
+      <c r="A569" s="1" t="n">
         <v>567</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="C569" s="3" t="n">
+      <c r="C569" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="D569" t="inlineStr">
@@ -35986,13 +35983,13 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="n">
+      <c r="A570" s="1" t="n">
         <v>568</v>
       </c>
       <c r="B570" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="C570" s="3" t="n">
+      <c r="C570" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="D570" t="inlineStr">
@@ -36044,13 +36041,13 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="n">
+      <c r="A571" s="1" t="n">
         <v>569</v>
       </c>
       <c r="B571" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="C571" s="3" t="n">
+      <c r="C571" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="D571" t="inlineStr">
@@ -36102,13 +36099,13 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="n">
+      <c r="A572" s="1" t="n">
         <v>570</v>
       </c>
       <c r="B572" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="C572" s="3" t="n">
+      <c r="C572" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D572" t="inlineStr">
@@ -36164,13 +36161,13 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="n">
+      <c r="A573" s="1" t="n">
         <v>571</v>
       </c>
       <c r="B573" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="C573" s="3" t="n">
+      <c r="C573" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D573" t="inlineStr">
@@ -36226,13 +36223,13 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="n">
+      <c r="A574" s="1" t="n">
         <v>572</v>
       </c>
       <c r="B574" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="C574" s="3" t="n">
+      <c r="C574" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D574" t="inlineStr">
@@ -36286,102 +36283,6 @@
       <c r="T574" t="n">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="n">
-        <v>573</v>
-      </c>
-      <c r="B575" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="C575" s="3" t="n">
-        <v>45627</v>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>Min.</t>
-        </is>
-      </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
-      <c r="G575" t="inlineStr"/>
-      <c r="H575" t="inlineStr"/>
-      <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
-      <c r="K575" t="inlineStr"/>
-      <c r="L575" t="inlineStr"/>
-      <c r="M575" t="inlineStr"/>
-      <c r="N575" t="inlineStr"/>
-      <c r="O575" t="inlineStr"/>
-      <c r="P575" t="inlineStr"/>
-      <c r="Q575" t="inlineStr"/>
-      <c r="R575" t="inlineStr"/>
-      <c r="S575" t="inlineStr"/>
-      <c r="T575" t="inlineStr"/>
-    </row>
-    <row r="576">
-      <c r="A576" t="n">
-        <v>574</v>
-      </c>
-      <c r="B576" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="C576" s="3" t="n">
-        <v>45627</v>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>Med.</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
-      <c r="G576" t="inlineStr"/>
-      <c r="H576" t="inlineStr"/>
-      <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
-      <c r="K576" t="inlineStr"/>
-      <c r="L576" t="inlineStr"/>
-      <c r="M576" t="inlineStr"/>
-      <c r="N576" t="inlineStr"/>
-      <c r="O576" t="inlineStr"/>
-      <c r="P576" t="inlineStr"/>
-      <c r="Q576" t="inlineStr"/>
-      <c r="R576" t="inlineStr"/>
-      <c r="S576" t="inlineStr"/>
-      <c r="T576" t="inlineStr"/>
-    </row>
-    <row r="577">
-      <c r="A577" t="n">
-        <v>575</v>
-      </c>
-      <c r="B577" s="2" t="n">
-        <v>45627</v>
-      </c>
-      <c r="C577" s="3" t="n">
-        <v>45627</v>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>Max.</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
-      <c r="H577" t="inlineStr"/>
-      <c r="I577" t="inlineStr"/>
-      <c r="J577" t="inlineStr"/>
-      <c r="K577" t="inlineStr"/>
-      <c r="L577" t="inlineStr"/>
-      <c r="M577" t="inlineStr"/>
-      <c r="N577" t="inlineStr"/>
-      <c r="O577" t="inlineStr"/>
-      <c r="P577" t="inlineStr"/>
-      <c r="Q577" t="inlineStr"/>
-      <c r="R577" t="inlineStr"/>
-      <c r="S577" t="inlineStr"/>
-      <c r="T577" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
